--- a/examples/results-rppa/pca/pca_norm_WT_7d_MC_CO_over_CO_CO.xlsx
+++ b/examples/results-rppa/pca/pca_norm_WT_7d_MC_CO_over_CO_CO.xlsx
@@ -1013,22 +1013,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0276825693382755</v>
+        <v>-0.0208760018062579</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0211724535325856</v>
+        <v>0.0337581227193334</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0731615203443069</v>
+        <v>-0.00993849099034437</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0127517825081079</v>
+        <v>0.0104687272453228</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00747364761466697</v>
+        <v>0.00228108650218073</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.521427227628303</v>
+        <v>-0.159798540011719</v>
       </c>
     </row>
     <row r="3">
@@ -1036,22 +1036,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0765748185770766</v>
+        <v>0.0183623798439114</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0885655945129855</v>
+        <v>-0.00798492783346628</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0239196194632948</v>
+        <v>-0.0253810112585595</v>
       </c>
       <c r="E3" t="n">
-        <v>0.205980098286069</v>
+        <v>-0.0317151457062741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.215975213240936</v>
+        <v>-0.018618837081751</v>
       </c>
       <c r="G3" t="n">
-        <v>0.343203555253933</v>
+        <v>-0.279329478605353</v>
       </c>
     </row>
     <row r="4">
@@ -1059,22 +1059,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00678234329368804</v>
+        <v>0.0378152670040101</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.014006517741787</v>
+        <v>-0.00680598251254102</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0212317212789788</v>
+        <v>0.00618982363404213</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.002619689857353</v>
+        <v>0.00759972778886281</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0112255726893321</v>
+        <v>0.0131942563358099</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.168357307791726</v>
+        <v>-0.150398646007047</v>
       </c>
     </row>
     <row r="5">
@@ -1082,22 +1082,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00331321324035305</v>
+        <v>0.0592089763780664</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0152662473538771</v>
+        <v>0.0125389443928777</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00658335240001044</v>
+        <v>-0.0378737657638692</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0110664611664607</v>
+        <v>0.00231636351444557</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0173515193109498</v>
+        <v>0.113541394602017</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.283999468001832</v>
+        <v>0.0203998088284591</v>
       </c>
     </row>
     <row r="6">
@@ -1105,22 +1105,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0000509600046739013</v>
+        <v>0.0000348650802898668</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000804526791891086</v>
+        <v>-0.00285396385120015</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00129412168110162</v>
+        <v>0.00738257832077002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00146532258153159</v>
+        <v>-0.0201250360373871</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00281177065824875</v>
+        <v>0.00880676158660602</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0469936971354454</v>
+        <v>-0.0835948080007354</v>
       </c>
     </row>
     <row r="7">
@@ -1128,22 +1128,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0215687407153822</v>
+        <v>0.0207274587143088</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0260599442250485</v>
+        <v>-0.00862068204093552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0183428629680627</v>
+        <v>-0.0112398320812323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0279711363450888</v>
+        <v>-0.00906222879016039</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000711023396867747</v>
+        <v>-0.0130596795873948</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0250643771124994</v>
+        <v>-0.132169048367387</v>
       </c>
     </row>
     <row r="8">
@@ -1151,22 +1151,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>0.00505929814436701</v>
+        <v>0.0197998722809281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00507796923646734</v>
+        <v>-0.0347557282016192</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00832751413973391</v>
+        <v>0.00774327797229524</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0160220359449674</v>
+        <v>-0.0432139030217731</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00176765647052885</v>
+        <v>-0.023790748357529</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0000373012610881296</v>
+        <v>-0.021594442971646</v>
       </c>
     </row>
     <row r="9">
@@ -1174,22 +1174,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0292275408895453</v>
+        <v>0.00862712659422254</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.20015529380772</v>
+        <v>0.0129320741799678</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.189086507668728</v>
+        <v>-0.0763050966577092</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.139515590872661</v>
+        <v>0.0129374353085661</v>
       </c>
       <c r="F9" t="n">
-        <v>0.525528169214343</v>
+        <v>0.0499468720497478</v>
       </c>
       <c r="G9" t="n">
-        <v>0.109707609483988</v>
+        <v>-0.0858828560181907</v>
       </c>
     </row>
     <row r="10">
@@ -1197,22 +1197,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0145685854089738</v>
+        <v>0.0532438609161521</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0265871831961695</v>
+        <v>-0.0109356359487019</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0136834352667431</v>
+        <v>-0.0315420247401537</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0182302264340943</v>
+        <v>0.00885968478520868</v>
       </c>
       <c r="F10" t="n">
-        <v>0.013014242340177</v>
+        <v>0.0410243519140937</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00151821011058408</v>
+        <v>0.137713154159151</v>
       </c>
     </row>
     <row r="11">
@@ -1220,22 +1220,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>0.061521442379591</v>
+        <v>-0.00914764024069908</v>
       </c>
       <c r="C11" t="n">
-        <v>0.308525851337568</v>
+        <v>-0.0355255107969785</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.117455739929356</v>
+        <v>-0.0086978540472488</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.339885190147641</v>
+        <v>0.0113794593134902</v>
       </c>
       <c r="F11" t="n">
-        <v>0.179383977161352</v>
+        <v>0.0184709334730005</v>
       </c>
       <c r="G11" t="n">
-        <v>0.190707665461421</v>
+        <v>-0.0876496372464789</v>
       </c>
     </row>
     <row r="12">
@@ -1243,22 +1243,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>0.011992306592935</v>
+        <v>0.0609066509539654</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0327593017267375</v>
+        <v>0.0123261948437374</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0121581661823683</v>
+        <v>-0.0436746074015156</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0444806422606235</v>
+        <v>-0.0725646823408849</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0376040940690423</v>
+        <v>-0.028146334043713</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0282222689575204</v>
+        <v>-0.0402445858620036</v>
       </c>
     </row>
     <row r="13">
@@ -1266,22 +1266,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.00189839235423252</v>
+        <v>-0.0395780660138576</v>
       </c>
       <c r="C13" t="n">
-        <v>0.011562671753286</v>
+        <v>-0.0313112969185558</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000647229020496858</v>
+        <v>0.0362263718454081</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.00369639460644266</v>
+        <v>-0.0289605332070667</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00452222499086087</v>
+        <v>0.026709470407761</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000827454443166908</v>
+        <v>-0.0470521767459831</v>
       </c>
     </row>
     <row r="14">
@@ -1289,22 +1289,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0117884064659979</v>
+        <v>-0.0232797218588173</v>
       </c>
       <c r="C14" t="n">
-        <v>0.201426715428458</v>
+        <v>-0.0320766177394105</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0299486531184472</v>
+        <v>0.0155785364783304</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.00756991406898277</v>
+        <v>-0.0222424653344163</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0391013930124157</v>
+        <v>0.0013217030487767</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0188373669225959</v>
+        <v>-0.136115408043986</v>
       </c>
     </row>
     <row r="15">
@@ -1312,22 +1312,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0854712153479282</v>
+        <v>0.00764539068208881</v>
       </c>
       <c r="C15" t="n">
-        <v>0.117707653473006</v>
+        <v>-0.036239283532378</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00353706810266253</v>
+        <v>-0.00490988454399399</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0326491060013185</v>
+        <v>-0.000374656178286835</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.00666966284073954</v>
+        <v>-0.00828614431847065</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.00531869378490039</v>
+        <v>-0.0428417039053138</v>
       </c>
     </row>
     <row r="16">
@@ -1335,22 +1335,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00211186392328762</v>
+        <v>0.0982028263249054</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0162376762393219</v>
+        <v>0.0535975863546412</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00569371704364006</v>
+        <v>-0.0596745667179995</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.00276969996965947</v>
+        <v>0.0145823009843295</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0104216661799166</v>
+        <v>-0.0354036828307205</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00357292731156196</v>
+        <v>0.00388346930171762</v>
       </c>
     </row>
     <row r="17">
@@ -1358,22 +1358,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00443118340496123</v>
+        <v>0.145908357188229</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.00846247137782759</v>
+        <v>-0.0162812402875757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00413066439610389</v>
+        <v>-0.0396840053748678</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.00749601912774621</v>
+        <v>0.019614763744093</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.00579417561045884</v>
+        <v>0.116561053744713</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00340195067111021</v>
+        <v>-0.0253885256442759</v>
       </c>
     </row>
     <row r="18">
@@ -1381,22 +1381,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.000143207837255406</v>
+        <v>0.0995929344366299</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.000289482282865005</v>
+        <v>0.0751329969170609</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00425511471462803</v>
+        <v>0.308743659926286</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00278122899903216</v>
+        <v>-0.0671344134746096</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.00325165021001935</v>
+        <v>0.124675440266002</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.000840138187925036</v>
+        <v>0.00755533716435296</v>
       </c>
     </row>
     <row r="19">
@@ -1404,22 +1404,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0334236885771244</v>
+        <v>0.036524947838877</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0657693363431272</v>
+        <v>-0.00285002809802077</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00938904014232353</v>
+        <v>-0.0339224436996225</v>
       </c>
       <c r="E19" t="n">
-        <v>0.031308171501512</v>
+        <v>-0.013609327855764</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0269045378166356</v>
+        <v>-0.0190987732284178</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0222667425955555</v>
+        <v>0.0478830706997344</v>
       </c>
     </row>
     <row r="20">
@@ -1427,22 +1427,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0161280988169752</v>
+        <v>0.0337494518288142</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.00912394949384531</v>
+        <v>-0.0265716198820313</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00535939857371316</v>
+        <v>-0.0233055413130218</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00109523093851844</v>
+        <v>-0.00219278299858002</v>
       </c>
       <c r="F20" t="n">
-        <v>0.000858677113988987</v>
+        <v>-0.0138300412100887</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.00465719764509262</v>
+        <v>0.00418798648651778</v>
       </c>
     </row>
     <row r="21">
@@ -1450,22 +1450,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>0.153358311385122</v>
+        <v>0.00720700689038557</v>
       </c>
       <c r="C21" t="n">
-        <v>0.164833419280238</v>
+        <v>-0.0301729783039426</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0572232548546579</v>
+        <v>-0.0094579626495031</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0342196867022111</v>
+        <v>0.0009707693809969</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0518107124976624</v>
+        <v>-0.0130768440180301</v>
       </c>
       <c r="G21" t="n">
-        <v>0.107565063918377</v>
+        <v>-0.133495086647652</v>
       </c>
     </row>
     <row r="22">
@@ -1473,22 +1473,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>0.00210837459191116</v>
+        <v>0.0398598507031057</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0124105045170501</v>
+        <v>0.0137664129787803</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00706595137838566</v>
+        <v>-0.0169296301361152</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.00837969573090601</v>
+        <v>0.0222986992410101</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00140252845065352</v>
+        <v>0.0504720958214279</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00834154384848146</v>
+        <v>0.0646872003396233</v>
       </c>
     </row>
     <row r="23">
@@ -1496,22 +1496,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0125691772123156</v>
+        <v>0.000414851094351515</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0199057902105829</v>
+        <v>-0.0331654912253849</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0191060672106752</v>
+        <v>-0.0170039734570512</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0189145692390905</v>
+        <v>0.0109490469346584</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.00199856617696452</v>
+        <v>-0.00801907206677721</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.018668323147505</v>
+        <v>-0.045163739656341</v>
       </c>
     </row>
     <row r="24">
@@ -1519,22 +1519,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0063327297713201</v>
+        <v>0.0389159369831637</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.00856318315510075</v>
+        <v>-0.013351823393849</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0111988567087371</v>
+        <v>-0.00622781482589078</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000876672068187647</v>
+        <v>-0.00387256554228681</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.000792279752531091</v>
+        <v>0.00812864990453763</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00740543558760876</v>
+        <v>0.00211344117200596</v>
       </c>
     </row>
     <row r="25">
@@ -1542,22 +1542,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>0.000839151211120376</v>
+        <v>-0.0239802218276091</v>
       </c>
       <c r="C25" t="n">
-        <v>0.22272959626195</v>
+        <v>-0.0453063572476477</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0458319766320991</v>
+        <v>0.0123250142051059</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0461508233236441</v>
+        <v>-0.0152532314111111</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0165571499100753</v>
+        <v>-0.000585826288109109</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0393873367270685</v>
+        <v>-0.137963025144238</v>
       </c>
     </row>
     <row r="26">
@@ -1565,22 +1565,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>0.000988180303892808</v>
+        <v>-0.0104560085710144</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0207792379268408</v>
+        <v>-0.0373063401192525</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00480180870719338</v>
+        <v>0.0213363194145413</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0204550683965642</v>
+        <v>0.0254974937121781</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.00534539145712081</v>
+        <v>0.0171827832771937</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.001318700048355</v>
+        <v>-0.0479909923683475</v>
       </c>
     </row>
     <row r="27">
@@ -1588,22 +1588,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>0.00615823173640281</v>
+        <v>-0.00924291062807264</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0710643286987361</v>
+        <v>-0.0233385669182958</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0192434626866728</v>
+        <v>-0.00191504160818083</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0220398355522033</v>
+        <v>-0.0110434512906988</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0640193232704782</v>
+        <v>0.0096518535602105</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0362931397378584</v>
+        <v>0.0438564238981407</v>
       </c>
     </row>
     <row r="28">
@@ -1611,22 +1611,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00600157245836643</v>
+        <v>0.00850339413836153</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0115631328028702</v>
+        <v>-0.00396669904747828</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0126686522273916</v>
+        <v>-0.0238791373813971</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0132944377523099</v>
+        <v>0.0254346071978451</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0166515605094609</v>
+        <v>-0.0137929423390177</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0255556942295567</v>
+        <v>0.0487322294211356</v>
       </c>
     </row>
     <row r="29">
@@ -1634,22 +1634,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>0.00234776063911071</v>
+        <v>0.0281924769209193</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.00959742368514602</v>
+        <v>0.015845054065128</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.00398866640409052</v>
+        <v>-0.0519159227307621</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00048738194557378</v>
+        <v>0.0224492191722621</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.00730295460195632</v>
+        <v>-0.0611252599689017</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00520246267415586</v>
+        <v>-0.0367382411729115</v>
       </c>
     </row>
     <row r="30">
@@ -1657,22 +1657,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>0.097787670068372</v>
+        <v>0.00468248314322546</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.00753163419513017</v>
+        <v>-0.0175422248773149</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.217227433654056</v>
+        <v>-0.0250541512129345</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.234645692914585</v>
+        <v>0.031619990941571</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.233785218462451</v>
+        <v>-0.0151375353943257</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.127759181223936</v>
+        <v>0.00276121267115479</v>
       </c>
     </row>
     <row r="31">
@@ -1680,22 +1680,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0489112478971166</v>
+        <v>0.0222663899264268</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0804843443845891</v>
+        <v>-0.00669882357446265</v>
       </c>
       <c r="D31" t="n">
-        <v>0.035675201388283</v>
+        <v>-0.0125356332633961</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00745271769708837</v>
+        <v>0.0079173707148955</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0780037650169939</v>
+        <v>-0.0155161965228446</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0647126438039566</v>
+        <v>-0.0436190372454803</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.00271197630100952</v>
+        <v>-0.0146848648857464</v>
       </c>
       <c r="C32" t="n">
-        <v>0.024568097282135</v>
+        <v>-0.0113317973403466</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.018906175607163</v>
+        <v>-0.00682291379482242</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000749869312303533</v>
+        <v>-0.0218430940924219</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0471491161295366</v>
+        <v>0.0114273423790247</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0164760869961832</v>
+        <v>-0.000345126388697046</v>
       </c>
     </row>
     <row r="33">
@@ -1726,22 +1726,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>0.015787351905113</v>
+        <v>-0.00443250415163518</v>
       </c>
       <c r="C33" t="n">
-        <v>0.435953799178284</v>
+        <v>-0.0232706194505161</v>
       </c>
       <c r="D33" t="n">
-        <v>0.270136389054802</v>
+        <v>0.0222995637640038</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.153922254313135</v>
+        <v>-0.00194300447017244</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0133902149465547</v>
+        <v>0.0119213100050439</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.00388570675331167</v>
+        <v>0.0421301182777997</v>
       </c>
     </row>
     <row r="34">
@@ -1749,22 +1749,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>0.00545634841342941</v>
+        <v>0.000170435153799856</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0114924460254505</v>
+        <v>-0.0130209987866863</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00456774987393936</v>
+        <v>-0.00899040473143104</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00364045547657315</v>
+        <v>-0.0174178221485046</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0484872274016671</v>
+        <v>0.00979635292545297</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0143614891174553</v>
+        <v>-0.043954894830194</v>
       </c>
     </row>
     <row r="35">
@@ -1772,22 +1772,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="n">
-        <v>0.139111144689523</v>
+        <v>0.0338551019767733</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0657657109116803</v>
+        <v>-0.0338355923931311</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0913805587824719</v>
+        <v>-0.0528776817399225</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0671293851479868</v>
+        <v>0.0143236793268724</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.00225825380947709</v>
+        <v>-0.0341889595902302</v>
       </c>
       <c r="G35" t="n">
-        <v>0.011379429181189</v>
+        <v>-0.044552539872446</v>
       </c>
     </row>
     <row r="36">
@@ -1795,22 +1795,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.00451964966530494</v>
+        <v>-0.326304145235387</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00597738425149205</v>
+        <v>0.104880919309591</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0171775472769649</v>
+        <v>-0.130637622772714</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.00295714412276278</v>
+        <v>-0.11437496648446</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0134102553747731</v>
+        <v>0.32899444797695</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00105653955183185</v>
+        <v>0.0151624129748573</v>
       </c>
     </row>
     <row r="37">
@@ -1818,22 +1818,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="n">
-        <v>0.00061911367602469</v>
+        <v>-0.00924872981034794</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00691981567467911</v>
+        <v>-0.00855410553257872</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0206450087278514</v>
+        <v>-0.0211096445469344</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0188451663970177</v>
+        <v>0.00831704403821472</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0229993397107255</v>
+        <v>0.0152194947953313</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0154136456604545</v>
+        <v>0.134467048287846</v>
       </c>
     </row>
     <row r="38">
@@ -1841,22 +1841,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0220556274004601</v>
+        <v>0.0381805211349343</v>
       </c>
       <c r="C38" t="n">
-        <v>0.00128505527126998</v>
+        <v>-0.0554768556997334</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.00377589305519871</v>
+        <v>-0.0331089848954672</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.00481112427313414</v>
+        <v>0.00574079442324913</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.00419455340744234</v>
+        <v>-0.0358323622482244</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.00416479043636188</v>
+        <v>-0.045433338755999</v>
       </c>
     </row>
     <row r="39">
@@ -1864,22 +1864,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="n">
-        <v>0.122839309103078</v>
+        <v>0.0148530766365049</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0766737271230612</v>
+        <v>-0.0420164115408248</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0512369460071714</v>
+        <v>-0.0216105602907027</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0274408027941005</v>
+        <v>-0.0112340656777645</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0513091695700046</v>
+        <v>-0.0213575034592113</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.10555929520662</v>
+        <v>0.0479861022806746</v>
       </c>
     </row>
     <row r="40">
@@ -1887,22 +1887,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0152592316406636</v>
+        <v>0.0054276980397218</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0217475015007014</v>
+        <v>-0.0347145673592191</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.00594499942408331</v>
+        <v>-0.0145203839790536</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0248798818438536</v>
+        <v>-0.0368322885452774</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0403343434157316</v>
+        <v>-0.0102502781410397</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0166985146617888</v>
+        <v>-0.089492803570622</v>
       </c>
     </row>
     <row r="41">
@@ -1933,22 +1933,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.000973256715964715</v>
+        <v>-0.0220032035925264</v>
       </c>
       <c r="C42" t="n">
-        <v>0.00127287104218882</v>
+        <v>-0.0045574019564066</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0139212152267534</v>
+        <v>-0.057556660082655</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.016881704266326</v>
+        <v>0.012228405169911</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0405030064631559</v>
+        <v>0.080966939673849</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.00261987564837956</v>
+        <v>-0.111885955074824</v>
       </c>
     </row>
     <row r="43">
@@ -1979,22 +1979,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.000847985482797923</v>
+        <v>-0.160250105715374</v>
       </c>
       <c r="C44" t="n">
-        <v>0.00535884494300051</v>
+        <v>-0.174929315701639</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0105000726424154</v>
+        <v>-0.161356414643375</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.00265744717258081</v>
+        <v>-0.263456319685706</v>
       </c>
       <c r="F44" t="n">
-        <v>0.00738230753541205</v>
+        <v>0.0694714923255936</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.000069089506623469</v>
+        <v>0.0559022642785683</v>
       </c>
     </row>
     <row r="45">
@@ -2002,22 +2002,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0213918245898569</v>
+        <v>0.0067602361102734</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0217491161570144</v>
+        <v>-0.00947763901270588</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0429883272567669</v>
+        <v>-0.0254861775342521</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0535009161347839</v>
+        <v>0.0227776044731429</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.0155516076437442</v>
+        <v>-0.00436639998047882</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.048820966837314</v>
+        <v>-0.134007695500133</v>
       </c>
     </row>
     <row r="46">
@@ -2025,22 +2025,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="n">
-        <v>0.00240962411616483</v>
+        <v>-0.00792532073603069</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00113131608397717</v>
+        <v>-0.0092910340171052</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0260966388138542</v>
+        <v>-0.0407272216285741</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.00118565907519806</v>
+        <v>-0.00783224237859152</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0239719821470185</v>
+        <v>-0.00528448060501928</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0140553416747953</v>
+        <v>-0.0420789807821445</v>
       </c>
     </row>
     <row r="47">
@@ -2048,22 +2048,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.00286543128428517</v>
+        <v>-0.242415343724695</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00290133026062083</v>
+        <v>0.0917594841653168</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0110854224664124</v>
+        <v>0.0566379319470165</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00394524292388773</v>
+        <v>-0.419241037994789</v>
       </c>
       <c r="F47" t="n">
-        <v>0.00924923056857003</v>
+        <v>0.0325111339542581</v>
       </c>
       <c r="G47" t="n">
-        <v>0.00108775090901578</v>
+        <v>-0.0266729523933783</v>
       </c>
     </row>
     <row r="48">
@@ -2071,22 +2071,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.00149737288498464</v>
+        <v>-0.18842868530257</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.00234854628407163</v>
+        <v>0.1977229714498</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.00943790486162223</v>
+        <v>-0.322152855130307</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00397139213230066</v>
+        <v>-0.185995869036626</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0116612450839616</v>
+        <v>-0.152195672531132</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0023913650981334</v>
+        <v>0.0319956582748591</v>
       </c>
     </row>
     <row r="49">
@@ -2094,22 +2094,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="n">
-        <v>0.00501755715695004</v>
+        <v>-0.0028812733339007</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00791988080073593</v>
+        <v>-0.015386840453191</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.0190606380987531</v>
+        <v>-0.0170065370072654</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0213709625552729</v>
+        <v>0.0181791186864575</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.00301044150065071</v>
+        <v>-0.000353439115425535</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00532677250848728</v>
+        <v>0.0448808190584647</v>
       </c>
     </row>
     <row r="50">
@@ -2117,22 +2117,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0844408454582513</v>
+        <v>0.0343284735599828</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0788986135668942</v>
+        <v>-0.0201512088396257</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.0117509730992056</v>
+        <v>-0.0355708915885148</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0082726300700193</v>
+        <v>0.00827457460412494</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0371664960544475</v>
+        <v>-0.0291487682026544</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0552552413967259</v>
+        <v>-0.040748564464416</v>
       </c>
     </row>
     <row r="51">
@@ -2140,22 +2140,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.000335952412595157</v>
+        <v>-0.0389667546450955</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0362748494357434</v>
+        <v>-0.0976804150732539</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00858061021019176</v>
+        <v>0.0455174374941205</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0244596073764708</v>
+        <v>-0.0135775515306906</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0143849583990403</v>
+        <v>0.0410564770801283</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.00648954093551123</v>
+        <v>0.0415134585066785</v>
       </c>
     </row>
     <row r="52">
@@ -2186,22 +2186,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0143312652763627</v>
+        <v>0.0167171255529731</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0011257828206341</v>
+        <v>-0.0271085141490038</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.00576854651824464</v>
+        <v>-0.0227414169207274</v>
       </c>
       <c r="E53" t="n">
-        <v>0.011625124665651</v>
+        <v>-0.0139500905731062</v>
       </c>
       <c r="F53" t="n">
-        <v>0.00684563796411446</v>
+        <v>-0.0242339318314376</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0102315237119043</v>
+        <v>-0.0890586328964932</v>
       </c>
     </row>
     <row r="54">
@@ -2209,22 +2209,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="n">
-        <v>0.00425616845526148</v>
+        <v>-0.0193274305015857</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0389597556821216</v>
+        <v>-0.0398345216505583</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0292385835839479</v>
+        <v>-0.0163409239243099</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0178238353591169</v>
+        <v>-0.00963756192084909</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0235340007719079</v>
+        <v>0.00499308422386937</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.00936492611792593</v>
+        <v>0.0902582293570758</v>
       </c>
     </row>
     <row r="55">
@@ -2232,22 +2232,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.00110981093562542</v>
+        <v>-0.0273497942754557</v>
       </c>
       <c r="C55" t="n">
-        <v>0.000182586863084159</v>
+        <v>0.0103696832619974</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.00795669992579274</v>
+        <v>-0.0457405966867437</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.00178387412422232</v>
+        <v>-0.00394910613259132</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00981517007074653</v>
+        <v>0.025205785246921</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000585591679213017</v>
+        <v>-0.0236733304351605</v>
       </c>
     </row>
     <row r="56">
@@ -2255,22 +2255,22 @@
         <v>61</v>
       </c>
       <c r="B56" t="n">
-        <v>0.00535238461513622</v>
+        <v>-0.00738979985735517</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0183835677037094</v>
+        <v>-0.0269925590778632</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0179748252872472</v>
+        <v>-0.0175734639089428</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0167342028244273</v>
+        <v>0.0029027906081667</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0168320363769942</v>
+        <v>0.0065487883967555</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.0095072087166612</v>
+        <v>0.00132089598527965</v>
       </c>
     </row>
     <row r="57">
@@ -2278,22 +2278,22 @@
         <v>62</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.00668680906504725</v>
+        <v>-0.068297515363803</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0148999550631592</v>
+        <v>0.011397148559435</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.0138543295534192</v>
+        <v>0.0136098090335235</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00253717944130636</v>
+        <v>-0.0790359250246404</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0211079861658232</v>
+        <v>0.0282891408368594</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.0039925896574085</v>
+        <v>0.0246602282442085</v>
       </c>
     </row>
     <row r="58">
@@ -2301,22 +2301,22 @@
         <v>63</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0000859344758380465</v>
+        <v>-0.00506813365705386</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0397602888822889</v>
+        <v>-0.00483506278939299</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.0772581857414151</v>
+        <v>0.00276207940911076</v>
       </c>
       <c r="E58" t="n">
-        <v>0.056725998522623</v>
+        <v>0.0123459404240059</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.262251246390235</v>
+        <v>-0.0439602998457358</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.0345638527160765</v>
+        <v>-0.042976502888346</v>
       </c>
     </row>
     <row r="59">
@@ -2324,22 +2324,22 @@
         <v>64</v>
       </c>
       <c r="B59" t="n">
-        <v>0.131583000226388</v>
+        <v>0.0246106821298752</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0446351304664248</v>
+        <v>-0.0282167902703308</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.0248660156774403</v>
+        <v>-0.0283379884350242</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0483437906384188</v>
+        <v>0.00397139121070977</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0407815491930021</v>
+        <v>-0.0111058918571693</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0490225376834867</v>
+        <v>-0.131305779688936</v>
       </c>
     </row>
     <row r="60">
@@ -2393,22 +2393,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="n">
-        <v>0.023709825989535</v>
+        <v>0.0133418779379515</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0060162005912335</v>
+        <v>-0.0159515383725231</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0124290369531995</v>
+        <v>-0.0138253945993512</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0296368685827376</v>
+        <v>0.000788949087649616</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0513390097688188</v>
+        <v>-0.0369831574011579</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.0261896301971211</v>
+        <v>0.00466507444412459</v>
       </c>
     </row>
     <row r="63">
@@ -2416,22 +2416,22 @@
         <v>68</v>
       </c>
       <c r="B63" t="n">
-        <v>0.00888282931210749</v>
+        <v>0.126494489702871</v>
       </c>
       <c r="C63" t="n">
-        <v>0.00246968784809759</v>
+        <v>-0.342014354954646</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.00733201648417559</v>
+        <v>-0.301633340711373</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.00992402212590534</v>
+        <v>0.113420602646903</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00560937074928505</v>
+        <v>-0.0346649440248383</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00160636426647609</v>
+        <v>-0.00325280237827187</v>
       </c>
     </row>
     <row r="64">
@@ -2439,22 +2439,22 @@
         <v>69</v>
       </c>
       <c r="B64" t="n">
-        <v>0.00350377343472345</v>
+        <v>-0.0304344272808897</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0079324985900454</v>
+        <v>-0.423272254296372</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00394024078324805</v>
+        <v>0.174297756020641</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.000586737066568175</v>
+        <v>-0.117128488932709</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00318181275098967</v>
+        <v>-0.108285981533543</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00242535735353514</v>
+        <v>0.0267461215156307</v>
       </c>
     </row>
     <row r="65">
@@ -2462,22 +2462,22 @@
         <v>70</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0336325473546213</v>
+        <v>0.0181752592285761</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00580089771933137</v>
+        <v>-0.0256489452555915</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0211003490069914</v>
+        <v>-0.00978660870607837</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0194816598767914</v>
+        <v>-0.0146192142314111</v>
       </c>
       <c r="F65" t="n">
-        <v>0.035399186334864</v>
+        <v>-0.00329777382993471</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.0122700954080599</v>
+        <v>0.135580074722973</v>
       </c>
     </row>
     <row r="66">
@@ -2508,22 +2508,22 @@
         <v>72</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.00497213261390975</v>
+        <v>-0.0231752087915032</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0110542248832749</v>
+        <v>0.00415399221025979</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.0098359437046658</v>
+        <v>0.00375784807766407</v>
       </c>
       <c r="E67" t="n">
-        <v>0.00379894779836668</v>
+        <v>-0.0246540555629402</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0169782971979848</v>
+        <v>0.00880642535804274</v>
       </c>
       <c r="G67" t="n">
-        <v>0.00124267541131764</v>
+        <v>-0.0915905691312245</v>
       </c>
     </row>
     <row r="68">
@@ -2531,22 +2531,22 @@
         <v>73</v>
       </c>
       <c r="B68" t="n">
-        <v>0.0264409419574244</v>
+        <v>0.0197238500847874</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.00954886759251682</v>
+        <v>-0.0243550029728403</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.0156377572659806</v>
+        <v>-0.0337851737641866</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.000917790242765589</v>
+        <v>-0.00730092265340927</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0343084909530385</v>
+        <v>-0.00974899721733256</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0279959557853313</v>
+        <v>-0.000145733139969747</v>
       </c>
     </row>
     <row r="69">
@@ -2554,22 +2554,22 @@
         <v>74</v>
       </c>
       <c r="B69" t="n">
-        <v>0.158448948633259</v>
+        <v>0.0138840835219039</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0340655281210544</v>
+        <v>-0.0259898965991531</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.0202410121881345</v>
+        <v>-0.015524535635877</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.0398651686012978</v>
+        <v>0.000345038313681736</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0454016650483877</v>
+        <v>-0.00818435298849425</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.212776201280917</v>
+        <v>-0.0459015945615333</v>
       </c>
     </row>
     <row r="70">
@@ -2577,22 +2577,22 @@
         <v>75</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.00262849241731223</v>
+        <v>-0.0273597722103579</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.00428050972425143</v>
+        <v>0.0589003795798018</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.00467743159907507</v>
+        <v>-0.0165700029837651</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.00792937070481149</v>
+        <v>0.0716677100561606</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.00320618253588556</v>
+        <v>0.041219087723614</v>
       </c>
       <c r="G70" t="n">
-        <v>0.00169616833730173</v>
+        <v>-0.00336326010945596</v>
       </c>
     </row>
     <row r="71">
@@ -2600,22 +2600,22 @@
         <v>76</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.000635325488219945</v>
+        <v>-0.00395314945775221</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.00281454019865383</v>
+        <v>0.00433285666929589</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.0110224921088904</v>
+        <v>-0.0121751734491371</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.00476667092072033</v>
+        <v>0.0122092625753547</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.00532523225742614</v>
+        <v>-0.00653473695086889</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.0059032926979628</v>
+        <v>0.0899787032720376</v>
       </c>
     </row>
     <row r="72">
@@ -2623,22 +2623,22 @@
         <v>77</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.00188670648928581</v>
+        <v>-0.0143323591659676</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.00455859748040279</v>
+        <v>0.0208489228177451</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.0198090281286169</v>
+        <v>-0.0392233280633393</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.000874661831035292</v>
+        <v>0.0241658279136815</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.00833972306460705</v>
+        <v>-0.0335746960100568</v>
       </c>
       <c r="G72" t="n">
-        <v>0.00467197317154741</v>
+        <v>-0.110710288565303</v>
       </c>
     </row>
     <row r="73">
@@ -2646,22 +2646,22 @@
         <v>78</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.00102980985957298</v>
+        <v>-0.0117854888788379</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0138229135513491</v>
+        <v>-0.0217283140093811</v>
       </c>
       <c r="D73" t="n">
-        <v>0.00674153985764851</v>
+        <v>0.0172263544186515</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.0151269048726433</v>
+        <v>0.00145268813296422</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0148039281489564</v>
+        <v>0.0455751799610975</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.00909422309246832</v>
+        <v>-0.047008415337235</v>
       </c>
     </row>
     <row r="74">
@@ -2669,22 +2669,22 @@
         <v>79</v>
       </c>
       <c r="B74" t="n">
-        <v>0.156830047766741</v>
+        <v>0.0366292526611145</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.0295898531059247</v>
+        <v>-0.027491103273396</v>
       </c>
       <c r="D74" t="n">
-        <v>0.296321434230564</v>
+        <v>0.00322057839161492</v>
       </c>
       <c r="E74" t="n">
-        <v>0.253171475176933</v>
+        <v>-0.032132910099214</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0976819320395591</v>
+        <v>0.00039683025897738</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.0716324929429822</v>
+        <v>-0.0866036070558792</v>
       </c>
     </row>
     <row r="75">
@@ -2692,22 +2692,22 @@
         <v>80</v>
       </c>
       <c r="B75" t="n">
-        <v>0.00347934687585455</v>
+        <v>0.0346232802471047</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0139584029369739</v>
+        <v>0.00361916133494962</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0368553801314752</v>
+        <v>0.0256070068349589</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00334695029620447</v>
+        <v>-0.0137209807312149</v>
       </c>
       <c r="F75" t="n">
-        <v>0.00208799004500885</v>
+        <v>0.0404741330939015</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0159250690043456</v>
+        <v>-0.133656931141269</v>
       </c>
     </row>
     <row r="76">
@@ -2715,22 +2715,22 @@
         <v>81</v>
       </c>
       <c r="B76" t="n">
-        <v>0.479126753269882</v>
+        <v>0.0788511531167245</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.363362374541357</v>
+        <v>-0.0378127982130221</v>
       </c>
       <c r="D76" t="n">
-        <v>0.11112157366747</v>
+        <v>-0.0486790330023498</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.214257666621223</v>
+        <v>0.00315129786512548</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0226685883295877</v>
+        <v>-0.00765274016529189</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0106948423909469</v>
+        <v>-0.0863444104377484</v>
       </c>
     </row>
     <row r="77">
@@ -2738,22 +2738,22 @@
         <v>82</v>
       </c>
       <c r="B77" t="n">
-        <v>0.00110421982496536</v>
+        <v>-0.00487760105624871</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0234782766810003</v>
+        <v>-0.0360732532159251</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0177942255546923</v>
+        <v>0.028457440436534</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.00848600101472405</v>
+        <v>-0.0211283136082273</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0210080037291365</v>
+        <v>0.036312302017858</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.00771348106967678</v>
+        <v>-0.0913009907852153</v>
       </c>
     </row>
     <row r="78">
@@ -2807,22 +2807,22 @@
         <v>85</v>
       </c>
       <c r="B80" t="n">
-        <v>0.189413615953207</v>
+        <v>0.0172705859301595</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0200529507866588</v>
+        <v>-0.0286923619359003</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.0167708578774929</v>
+        <v>-0.0138959895229747</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.0410970164930878</v>
+        <v>0.0100257501550315</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.206760179807163</v>
+        <v>-0.0220726110340775</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0943551540355553</v>
+        <v>0.136898463337386</v>
       </c>
     </row>
     <row r="81">
@@ -2830,22 +2830,22 @@
         <v>86</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0371483409128615</v>
+        <v>-0.00223867338422318</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0984676866431732</v>
+        <v>-0.0223442915034916</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.0716423222263041</v>
+        <v>-0.0120515239010618</v>
       </c>
       <c r="E81" t="n">
-        <v>0.19503377042441</v>
+        <v>-0.0413242563459515</v>
       </c>
       <c r="F81" t="n">
-        <v>0.154182020924526</v>
+        <v>-0.0213004082185207</v>
       </c>
       <c r="G81" t="n">
-        <v>0.000880341764392871</v>
+        <v>0.0924982924372281</v>
       </c>
     </row>
     <row r="82">
@@ -2853,22 +2853,22 @@
         <v>87</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0753362999458342</v>
+        <v>0.0198806732003108</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.0581009749687625</v>
+        <v>-0.0151339287876037</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.0553805115511532</v>
+        <v>-0.0302786730377277</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0661947687084038</v>
+        <v>-0.0052085994035326</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.0180871892576206</v>
+        <v>-0.035199955001898</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.0123395061253228</v>
+        <v>-0.0842635023653809</v>
       </c>
     </row>
     <row r="83">
@@ -2876,22 +2876,22 @@
         <v>88</v>
       </c>
       <c r="B83" t="n">
-        <v>-0.00120409209995379</v>
+        <v>0.0372565045104934</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.0167660674447733</v>
+        <v>0.105767965956893</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.00980771702252278</v>
+        <v>-0.116544275069037</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0198533168061013</v>
+        <v>-0.0829602052973178</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0165056916492969</v>
+        <v>-0.215747861235874</v>
       </c>
       <c r="G83" t="n">
-        <v>0.00685211462809131</v>
+        <v>0.00412419328288507</v>
       </c>
     </row>
     <row r="84">
@@ -2899,22 +2899,22 @@
         <v>89</v>
       </c>
       <c r="B84" t="n">
-        <v>0.232909944655866</v>
+        <v>0.0248300138388304</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.0388708933975742</v>
+        <v>-0.0277979783323756</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0575633783187</v>
+        <v>-0.017659160390724</v>
       </c>
       <c r="E84" t="n">
-        <v>0.146773767512981</v>
+        <v>-0.0106880855707229</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0255455598776555</v>
+        <v>-0.0203074398929993</v>
       </c>
       <c r="G84" t="n">
-        <v>0.061424453139422</v>
+        <v>-0.0437577209575399</v>
       </c>
     </row>
     <row r="85">
@@ -2945,22 +2945,22 @@
         <v>91</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.000664316368654586</v>
+        <v>0.00768947867952487</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.00621154528090122</v>
+        <v>0.0194776223110358</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00275700301380322</v>
+        <v>-0.00206583249295196</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0125754837578723</v>
+        <v>-0.0383145170700204</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0129218687605192</v>
+        <v>-0.000971623869874352</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.00138572920175613</v>
+        <v>-0.0651505430976553</v>
       </c>
     </row>
     <row r="87">
@@ -2968,22 +2968,22 @@
         <v>92</v>
       </c>
       <c r="B87" t="n">
-        <v>0.00366681431894123</v>
+        <v>0.0206804259461649</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.0113530716630786</v>
+        <v>0.00354369260503934</v>
       </c>
       <c r="D87" t="n">
-        <v>0.000917622103685597</v>
+        <v>-0.0215699618324649</v>
       </c>
       <c r="E87" t="n">
-        <v>0.00285630678820068</v>
+        <v>-0.00293461448079394</v>
       </c>
       <c r="F87" t="n">
-        <v>0.00344312214302489</v>
+        <v>-0.00798493433834989</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.00319299323999896</v>
+        <v>0.0470344237469123</v>
       </c>
     </row>
     <row r="88">
@@ -2991,22 +2991,22 @@
         <v>93</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0173308268767945</v>
+        <v>0.0456438862606309</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.0425430374630474</v>
+        <v>0.00573801747415641</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0150986456284039</v>
+        <v>-0.0338348870177088</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0540449100038253</v>
+        <v>-0.0482767970831123</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0380160948681855</v>
+        <v>-0.0269609465227367</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.000024051139884026</v>
+        <v>0.0498368155442937</v>
       </c>
     </row>
     <row r="89">
@@ -3014,22 +3014,22 @@
         <v>94</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0668286539209239</v>
+        <v>0.0144118901280012</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0195281289532571</v>
+        <v>-0.0228798570176672</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0176715191847179</v>
+        <v>-0.0074000186042987</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0873577160300889</v>
+        <v>-0.00929785456864268</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.0511210855377095</v>
+        <v>-0.0248667857801995</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.0606023346375438</v>
+        <v>0.0916300422932872</v>
       </c>
     </row>
     <row r="90">
@@ -3037,22 +3037,22 @@
         <v>95</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0194124260629797</v>
+        <v>0.0280975160556019</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.0285625990582949</v>
+        <v>-0.00783782050269054</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0198883181944253</v>
+        <v>-0.014804882569001</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0246522714782637</v>
+        <v>-0.0140481745701567</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0106033349007502</v>
+        <v>-0.0100675514677194</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.0289314526385774</v>
+        <v>0.0911890471651078</v>
       </c>
     </row>
     <row r="91">
@@ -3060,22 +3060,22 @@
         <v>96</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.00116221879989696</v>
+        <v>0.00656532754817305</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.0113823147664364</v>
+        <v>0.0696013691066277</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0057706029683258</v>
+        <v>-0.0622503062191574</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.00212302205871453</v>
+        <v>0.0467909007629623</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.00304634652947259</v>
+        <v>-0.0329277643623355</v>
       </c>
       <c r="G91" t="n">
-        <v>0.00513201493988945</v>
+        <v>-0.0425228386699796</v>
       </c>
     </row>
     <row r="92">
@@ -3083,22 +3083,22 @@
         <v>97</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.000628768176701828</v>
+        <v>-0.0132515275169445</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.00479310243138413</v>
+        <v>0.336721734860029</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.000809698957597331</v>
+        <v>-0.18623943126285</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.00104116584264948</v>
+        <v>0.166718188381516</v>
       </c>
       <c r="F92" t="n">
-        <v>0.00111586495760083</v>
+        <v>-0.0326620185868539</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00115376767115136</v>
+        <v>0.00202343509710424</v>
       </c>
     </row>
     <row r="93">
@@ -3152,22 +3152,22 @@
         <v>100</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.00394538690954714</v>
+        <v>-0.00830942562108276</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0163402189758913</v>
+        <v>-0.00350704433661308</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0145081461573483</v>
+        <v>0.0191335975974929</v>
       </c>
       <c r="E95" t="n">
-        <v>0.00785286842781053</v>
+        <v>-0.0324505445272487</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0357833836522088</v>
+        <v>0.0250755349299831</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.0219934295949244</v>
+        <v>-0.0444053161746636</v>
       </c>
     </row>
     <row r="96">
@@ -3175,22 +3175,22 @@
         <v>101</v>
       </c>
       <c r="B96" t="n">
-        <v>0.00282928455799576</v>
+        <v>0.00129868759429332</v>
       </c>
       <c r="C96" t="n">
-        <v>0.00840467416446229</v>
+        <v>-0.0264395676724851</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0022012005160663</v>
+        <v>-0.000140892161335468</v>
       </c>
       <c r="E96" t="n">
-        <v>0.00479474568146807</v>
+        <v>-0.0276420338935352</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0121524766575147</v>
+        <v>0.00378792449807149</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00564390731991449</v>
+        <v>0.00037763539978702</v>
       </c>
     </row>
     <row r="97">
@@ -3198,22 +3198,22 @@
         <v>102</v>
       </c>
       <c r="B97" t="n">
-        <v>0.129327608781627</v>
+        <v>0.0110738055452453</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0395072526525878</v>
+        <v>-0.0194912886317988</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0440212218990949</v>
+        <v>-0.00579006119516481</v>
       </c>
       <c r="E97" t="n">
-        <v>0.00131035031866356</v>
+        <v>0.00218188481954045</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.0986767842796971</v>
+        <v>-0.0102043064709931</v>
       </c>
       <c r="G97" t="n">
-        <v>0.147406253491754</v>
+        <v>-0.0887779305952718</v>
       </c>
     </row>
     <row r="98">
@@ -3221,22 +3221,22 @@
         <v>103</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.0196234909198611</v>
+        <v>0.00397872317913428</v>
       </c>
       <c r="C98" t="n">
-        <v>0.209644310641757</v>
+        <v>-0.0275489395726656</v>
       </c>
       <c r="D98" t="n">
-        <v>0.356952840546973</v>
+        <v>0.0672622630413475</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.224745265990582</v>
+        <v>-0.0113784034920152</v>
       </c>
       <c r="F98" t="n">
-        <v>0.261049586720764</v>
+        <v>0.0957075456321249</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.18538906034108</v>
+        <v>0.0342223061794475</v>
       </c>
     </row>
     <row r="99">
@@ -3244,22 +3244,22 @@
         <v>104</v>
       </c>
       <c r="B99" t="n">
-        <v>0.000461067973229492</v>
+        <v>0.204107966576081</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.00530520405391239</v>
+        <v>0.0923266036137357</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0032059960819173</v>
+        <v>-0.0446463255108671</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00557253993683335</v>
+        <v>-0.205111295540567</v>
       </c>
       <c r="F99" t="n">
-        <v>0.00198621843424316</v>
+        <v>0.0714911381364169</v>
       </c>
       <c r="G99" t="n">
-        <v>0.00179433654875994</v>
+        <v>0.045540768310658</v>
       </c>
     </row>
     <row r="100">
@@ -3267,22 +3267,22 @@
         <v>105</v>
       </c>
       <c r="B100" t="n">
-        <v>0.00116731257680616</v>
+        <v>0.281727317691547</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.014571391539978</v>
+        <v>0.149564490665699</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00532237658186128</v>
+        <v>-0.166342937730652</v>
       </c>
       <c r="E100" t="n">
-        <v>0.00579186971696076</v>
+        <v>-0.213504840056701</v>
       </c>
       <c r="F100" t="n">
-        <v>0.00097092891401909</v>
+        <v>-0.1113117209935</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00491931057897072</v>
+        <v>-0.0655566066654908</v>
       </c>
     </row>
     <row r="101">
@@ -3290,22 +3290,22 @@
         <v>106</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0302720007410355</v>
+        <v>0.0439345394576783</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0126733735541829</v>
+        <v>-0.0510093870875176</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0501644938699472</v>
+        <v>0.0101015254455375</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0289494176076786</v>
+        <v>-0.0395085236569034</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0251194563081605</v>
+        <v>0.0156047289864664</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.0123352762686612</v>
+        <v>0.00348089254676056</v>
       </c>
     </row>
     <row r="102">
@@ -3313,22 +3313,22 @@
         <v>107</v>
       </c>
       <c r="B102" t="n">
-        <v>0.0094676766058713</v>
+        <v>0.00824757881119759</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0010151699055901</v>
+        <v>-0.0158924495114562</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.00654247307262877</v>
+        <v>-0.0126102154052459</v>
       </c>
       <c r="E102" t="n">
-        <v>0.00213154164636906</v>
+        <v>0.00230131602105449</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.00828674595216278</v>
+        <v>-0.0165223712653624</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.00147712201703917</v>
+        <v>0.09176614875499</v>
       </c>
     </row>
     <row r="103">
@@ -3336,22 +3336,22 @@
         <v>108</v>
       </c>
       <c r="B103" t="n">
-        <v>0.00284046054868401</v>
+        <v>0.00100428700194261</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0139556000130681</v>
+        <v>-0.0320451969592129</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00915872886453525</v>
+        <v>0.0169795750129315</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.00584964734037852</v>
+        <v>-0.00222263319693046</v>
       </c>
       <c r="F103" t="n">
-        <v>0.00284710555028085</v>
+        <v>0.0126895573808783</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.00911946196610814</v>
+        <v>-0.0894530581053949</v>
       </c>
     </row>
     <row r="104">
@@ -3359,22 +3359,22 @@
         <v>109</v>
       </c>
       <c r="B104" t="n">
-        <v>0.000881819135293905</v>
+        <v>0.202275119365921</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.00795576918678145</v>
+        <v>0.0559083822990537</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00432617382441175</v>
+        <v>-0.0100658412403664</v>
       </c>
       <c r="E104" t="n">
-        <v>0.00489014182589864</v>
+        <v>-0.194154816383981</v>
       </c>
       <c r="F104" t="n">
-        <v>0.00671190390676107</v>
+        <v>0.267991167228072</v>
       </c>
       <c r="G104" t="n">
-        <v>0.000218488652900921</v>
+        <v>0.0346427005478229</v>
       </c>
     </row>
     <row r="105">
@@ -3382,22 +3382,22 @@
         <v>110</v>
       </c>
       <c r="B105" t="n">
-        <v>0.00321957716438319</v>
+        <v>0.109187046865428</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.0101688834534511</v>
+        <v>0.0116075504744826</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00737015651376266</v>
+        <v>-0.0209654109664058</v>
       </c>
       <c r="E105" t="n">
-        <v>0.00192383624194516</v>
+        <v>-0.0584655049484297</v>
       </c>
       <c r="F105" t="n">
-        <v>0.00363679411893689</v>
+        <v>0.0901616077627789</v>
       </c>
       <c r="G105" t="n">
-        <v>0.00115962230354269</v>
+        <v>-0.0671457866933146</v>
       </c>
     </row>
     <row r="106">
@@ -3405,22 +3405,22 @@
         <v>111</v>
       </c>
       <c r="B106" t="n">
-        <v>0.00780779454041253</v>
+        <v>0.039928358607264</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.00478560022019712</v>
+        <v>-0.0208119992448072</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0291984838739418</v>
+        <v>0.0173497427945694</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.00276873934081541</v>
+        <v>-0.0127797759001378</v>
       </c>
       <c r="F106" t="n">
-        <v>0.00887564747712853</v>
+        <v>0.0465829442138955</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.00755629808551286</v>
+        <v>-0.000138363346590765</v>
       </c>
     </row>
     <row r="107">
@@ -3428,22 +3428,22 @@
         <v>112</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.00271918573644062</v>
+        <v>-0.0321896379959616</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00393391984498072</v>
+        <v>0.0191422860305271</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.00488406852067725</v>
+        <v>0.0138937082889285</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0017476566716719</v>
+        <v>-0.0183225640827699</v>
       </c>
       <c r="F107" t="n">
-        <v>0.00102601762433005</v>
+        <v>-0.00139010832855707</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0000523581077562188</v>
+        <v>0.0203277996605591</v>
       </c>
     </row>
     <row r="108">
@@ -3451,22 +3451,22 @@
         <v>113</v>
       </c>
       <c r="B108" t="n">
-        <v>-0.000184291439122099</v>
+        <v>0.102112263485813</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.00347851855739053</v>
+        <v>0.178794583784247</v>
       </c>
       <c r="D108" t="n">
-        <v>0.00190733661218214</v>
+        <v>0.0669838144096066</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.0028024676621706</v>
+        <v>0.365371521792395</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.00645604107873214</v>
+        <v>-0.00217462071176539</v>
       </c>
       <c r="G108" t="n">
-        <v>0.000935928061128599</v>
+        <v>-0.0238353581025469</v>
       </c>
     </row>
     <row r="109">
@@ -3474,22 +3474,22 @@
         <v>114</v>
       </c>
       <c r="B109" t="n">
-        <v>0.00227319004545942</v>
+        <v>0.118046775221005</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.0147372073435723</v>
+        <v>0.0207150813409663</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0189059160322169</v>
+        <v>0.0317082661521877</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.00169172746231932</v>
+        <v>-0.0621753806464647</v>
       </c>
       <c r="F109" t="n">
-        <v>0.00190294931540064</v>
+        <v>0.188434674336212</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0043113854332718</v>
+        <v>-0.0333397981056795</v>
       </c>
     </row>
     <row r="110">
@@ -3497,22 +3497,22 @@
         <v>115</v>
       </c>
       <c r="B110" t="n">
-        <v>0.128049436605176</v>
+        <v>0.011809992050328</v>
       </c>
       <c r="C110" t="n">
-        <v>0.064464690218728</v>
+        <v>-0.0218071018459441</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0736057940744365</v>
+        <v>-0.00221192414393415</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0567813144139871</v>
+        <v>0.000375479326064364</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.158208748392043</v>
+        <v>-0.0149856350553797</v>
       </c>
       <c r="G110" t="n">
-        <v>0.152731507430604</v>
+        <v>0.0905921423198863</v>
       </c>
     </row>
     <row r="111">
@@ -3520,22 +3520,22 @@
         <v>116</v>
       </c>
       <c r="B111" t="n">
-        <v>0.108849977861149</v>
+        <v>0.00476069909626213</v>
       </c>
       <c r="C111" t="n">
-        <v>0.110949999270397</v>
+        <v>-0.0220721706942494</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.104834089376914</v>
+        <v>-0.0122270365082954</v>
       </c>
       <c r="E111" t="n">
-        <v>0.110803058824833</v>
+        <v>-0.0092900998365682</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0139818492455044</v>
+        <v>-0.0186419734758128</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0608345722979218</v>
+        <v>0.0463993934844458</v>
       </c>
     </row>
     <row r="112">
@@ -3543,22 +3543,22 @@
         <v>117</v>
       </c>
       <c r="B112" t="n">
-        <v>0.00232231877815986</v>
+        <v>0.0965376163651931</v>
       </c>
       <c r="C112" t="n">
-        <v>0.000645672934186945</v>
+        <v>-0.261017303343067</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.00191687568956999</v>
+        <v>-0.230199463999935</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.00259452727594919</v>
+        <v>0.0865599335746182</v>
       </c>
       <c r="F112" t="n">
-        <v>0.00146650876280709</v>
+        <v>-0.0264554691311173</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0000590022945107045</v>
+        <v>0.0184882675174324</v>
       </c>
     </row>
     <row r="113">
@@ -3566,22 +3566,22 @@
         <v>118</v>
       </c>
       <c r="B113" t="n">
-        <v>0.00123623326094247</v>
+        <v>0.0222733162321837</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.0154948874538006</v>
+        <v>0.0214875176853009</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00452353962140417</v>
+        <v>-0.0144790670807686</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0072061858463407</v>
+        <v>-0.0134282135463501</v>
       </c>
       <c r="F113" t="n">
-        <v>0.00613173483286196</v>
+        <v>-0.00261155786870762</v>
       </c>
       <c r="G113" t="n">
-        <v>0.00377171508697624</v>
+        <v>0.0893224830216871</v>
       </c>
     </row>
     <row r="114">
@@ -3589,22 +3589,22 @@
         <v>119</v>
       </c>
       <c r="B114" t="n">
-        <v>0.218673626851959</v>
+        <v>0.0243547771728981</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0814025103261341</v>
+        <v>-0.03150573223893</v>
       </c>
       <c r="D114" t="n">
-        <v>0.329344212570436</v>
+        <v>0.00533829201957185</v>
       </c>
       <c r="E114" t="n">
-        <v>0.244943412380899</v>
+        <v>-0.0145606881946141</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.0788438877826441</v>
+        <v>-0.0117127960253572</v>
       </c>
       <c r="G114" t="n">
-        <v>0.20004578772942</v>
+        <v>0.094433037230671</v>
       </c>
     </row>
     <row r="115">
@@ -3612,22 +3612,22 @@
         <v>120</v>
       </c>
       <c r="B115" t="n">
-        <v>0.0373027215387704</v>
+        <v>-0.00281590895334617</v>
       </c>
       <c r="C115" t="n">
-        <v>0.098567894125862</v>
+        <v>-0.0178197742238294</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.118422620575167</v>
+        <v>-0.0110055692444259</v>
       </c>
       <c r="E115" t="n">
-        <v>0.116170076264503</v>
+        <v>-0.0152392502180126</v>
       </c>
       <c r="F115" t="n">
-        <v>0.00738212525085042</v>
+        <v>-0.0230843983494457</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0374992992249649</v>
+        <v>0.0904948018378706</v>
       </c>
     </row>
     <row r="116">
@@ -3635,22 +3635,22 @@
         <v>121</v>
       </c>
       <c r="B116" t="n">
-        <v>0.0406922166413874</v>
+        <v>0.00852118779704109</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0283523382370376</v>
+        <v>-0.022359076417885</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.01804776801872</v>
+        <v>-0.0110247204264064</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0673977688054958</v>
+        <v>-0.0143262737563715</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.00398165395700239</v>
+        <v>-0.0244193586574639</v>
       </c>
       <c r="G116" t="n">
-        <v>0.064321782739379</v>
+        <v>0.0463414221184031</v>
       </c>
     </row>
     <row r="117">
@@ -3658,22 +3658,22 @@
         <v>122</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0142226829265962</v>
+        <v>0.0186864802532223</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00370145440582888</v>
+        <v>-0.0237554663482267</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0189437148849075</v>
+        <v>-0.000130874954076214</v>
       </c>
       <c r="E117" t="n">
-        <v>0.014669151634348</v>
+        <v>-0.0137521065678475</v>
       </c>
       <c r="F117" t="n">
-        <v>0.00374603935590681</v>
+        <v>-0.00624037043541169</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.00476874072558564</v>
+        <v>-0.0448114459698023</v>
       </c>
     </row>
     <row r="118">
@@ -3704,22 +3704,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0215532333696972</v>
+        <v>0.00437371785159518</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0477321927834867</v>
+        <v>-0.0225902532313866</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0261549343230708</v>
+        <v>0.00249407757036373</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0224839059810428</v>
+        <v>-0.0157217262923958</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0434344554945222</v>
+        <v>0.000895720509625823</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0251920233278121</v>
+        <v>-0.044363018973753</v>
       </c>
     </row>
     <row r="120">
@@ -3727,22 +3727,22 @@
         <v>125</v>
       </c>
       <c r="B120" t="n">
-        <v>0.0766388062502145</v>
+        <v>0.0304961359630437</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0524255588023965</v>
+        <v>-0.0604695115560925</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0512414070796037</v>
+        <v>-0.000650686986294585</v>
       </c>
       <c r="E120" t="n">
-        <v>0.038570780329264</v>
+        <v>-0.018405850623779</v>
       </c>
       <c r="F120" t="n">
-        <v>0.000768295863369202</v>
+        <v>-0.0190717132582681</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0961328015281166</v>
+        <v>0.0899260121506821</v>
       </c>
     </row>
     <row r="121">
@@ -3750,22 +3750,22 @@
         <v>126</v>
       </c>
       <c r="B121" t="n">
-        <v>0.0116868360692265</v>
+        <v>0.00949897952855844</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00398059292257366</v>
+        <v>-0.0186777082904124</v>
       </c>
       <c r="D121" t="n">
-        <v>0.00179150544075127</v>
+        <v>-0.00890958566006731</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.00403677060001936</v>
+        <v>-0.000436878326329391</v>
       </c>
       <c r="F121" t="n">
-        <v>0.00648571529929523</v>
+        <v>-0.00199203742021849</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.0274325311227473</v>
+        <v>-0.0888783508285495</v>
       </c>
     </row>
     <row r="122">
@@ -3773,22 +3773,22 @@
         <v>127</v>
       </c>
       <c r="B122" t="n">
-        <v>0.0186408957926078</v>
+        <v>-0.0116832562513509</v>
       </c>
       <c r="C122" t="n">
-        <v>0.250404641860049</v>
+        <v>-0.0193913163288249</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.239451456800347</v>
+        <v>-0.0100796930213195</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.0776227143802889</v>
+        <v>-0.0039451430065742</v>
       </c>
       <c r="F122" t="n">
-        <v>0.115724105368708</v>
+        <v>-0.00226787560494046</v>
       </c>
       <c r="G122" t="n">
-        <v>0.230388965934418</v>
+        <v>0.0902257710905345</v>
       </c>
     </row>
     <row r="123">
@@ -3796,22 +3796,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="n">
-        <v>0.0195172456106307</v>
+        <v>0.0420444127228009</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.00398100134949792</v>
+        <v>-0.0354082084124411</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0213241510725747</v>
+        <v>-0.00796990046096838</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0157821435773328</v>
+        <v>-0.0256439129387366</v>
       </c>
       <c r="F123" t="n">
-        <v>0.00919376762368028</v>
+        <v>-0.0030945516940245</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.0192480861247486</v>
+        <v>0.0466706044676657</v>
       </c>
     </row>
     <row r="124">
@@ -3819,22 +3819,22 @@
         <v>129</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.0000464016226200225</v>
+        <v>0.214509476937469</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.00709668769134699</v>
+        <v>0.169949706522856</v>
       </c>
       <c r="D124" t="n">
-        <v>0.00303427303857668</v>
+        <v>-0.0986900598217087</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.000728124936937832</v>
+        <v>-0.0914008266838585</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.00482323921100485</v>
+        <v>-0.0683879583768455</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00156366108495006</v>
+        <v>-0.00672647672479234</v>
       </c>
     </row>
     <row r="125">
@@ -3842,22 +3842,22 @@
         <v>130</v>
       </c>
       <c r="B125" t="n">
-        <v>0.00327206251682285</v>
+        <v>0.0162325684935257</v>
       </c>
       <c r="C125" t="n">
-        <v>0.000176720768606665</v>
+        <v>-0.0150534475190431</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0097772821274672</v>
+        <v>0.0113617341823124</v>
       </c>
       <c r="E125" t="n">
-        <v>0.00243615951459646</v>
+        <v>-0.000449901553248007</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.00634633821864678</v>
+        <v>-0.00372098339390614</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.00785829351990528</v>
+        <v>-0.0450115581503963</v>
       </c>
     </row>
     <row r="126">
@@ -3865,22 +3865,22 @@
         <v>131</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0541191406371636</v>
+        <v>0.0111430659700834</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.0067566069521565</v>
+        <v>-0.0179441122518211</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.0361560666272815</v>
+        <v>-0.0186601092883804</v>
       </c>
       <c r="E126" t="n">
-        <v>0.00317584883781497</v>
+        <v>0.000265083979337304</v>
       </c>
       <c r="F126" t="n">
-        <v>0.00619061745577232</v>
+        <v>-0.0139729795998599</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.0490294022642972</v>
+        <v>0.137145478603422</v>
       </c>
     </row>
     <row r="127">
@@ -3888,22 +3888,22 @@
         <v>132</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.00375395571167915</v>
+        <v>-0.010741922669771</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0368353885805465</v>
+        <v>-0.00786290563955333</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.057657540199764</v>
+        <v>-0.00366024631782151</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.0558955818980589</v>
+        <v>0.0260054036229405</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.087826268013708</v>
+        <v>-0.00910867969887503</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0704295346702612</v>
+        <v>0.090326113640403</v>
       </c>
     </row>
     <row r="128">
@@ -3911,22 +3911,22 @@
         <v>133</v>
       </c>
       <c r="B128" t="n">
-        <v>0.0000560630153886338</v>
+        <v>0.131481738008626</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.000230597345516154</v>
+        <v>0.106163932687775</v>
       </c>
       <c r="D128" t="n">
-        <v>0.00332448671475861</v>
+        <v>0.271126731888413</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0052828229095349</v>
+        <v>-0.0842559256894294</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.0037172070799209</v>
+        <v>-0.273243057178281</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.00047648829723966</v>
+        <v>-0.00668424852547456</v>
       </c>
     </row>
     <row r="129">
@@ -3934,22 +3934,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="n">
-        <v>0.058532079139278</v>
+        <v>0.0108140611444156</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0406022225367392</v>
+        <v>-0.0322413778444468</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.0246818603764394</v>
+        <v>-0.0177226768573701</v>
       </c>
       <c r="E129" t="n">
-        <v>0.027167630785001</v>
+        <v>-0.0142776366806685</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0558718578124626</v>
+        <v>-0.0137446492311143</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0360047240711862</v>
+        <v>-0.0868436862334136</v>
       </c>
     </row>
     <row r="130">
@@ -3957,22 +3957,22 @@
         <v>135</v>
       </c>
       <c r="B130" t="n">
-        <v>0.152000081563848</v>
+        <v>0.0144635615092941</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0586788459176472</v>
+        <v>-0.0262740442653458</v>
       </c>
       <c r="D130" t="n">
-        <v>0.0795921214315894</v>
+        <v>-0.00904825040094726</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.0539242720221353</v>
+        <v>-0.00420256093180313</v>
       </c>
       <c r="F130" t="n">
-        <v>0.154203305776235</v>
+        <v>0.00379896578787164</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.143470298052286</v>
+        <v>0.0924898222144486</v>
       </c>
     </row>
     <row r="131">
@@ -3980,22 +3980,22 @@
         <v>136</v>
       </c>
       <c r="B131" t="n">
-        <v>0.00737066106249149</v>
+        <v>0.0290468866011963</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.0199656588454146</v>
+        <v>-0.000775207108102059</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0211887640663041</v>
+        <v>0.00165286839185729</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.000179680199219791</v>
+        <v>0.0113428594888185</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.0234976414542775</v>
+        <v>-0.0052142683942725</v>
       </c>
       <c r="G131" t="n">
-        <v>0.00904358352055415</v>
+        <v>0.135341549223006</v>
       </c>
     </row>
     <row r="132">
@@ -4003,22 +4003,22 @@
         <v>137</v>
       </c>
       <c r="B132" t="n">
-        <v>0.00953404789683541</v>
+        <v>0.00251771681973988</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0163629277989551</v>
+        <v>-0.0395014003938543</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.00840233365046272</v>
+        <v>-0.0115262332304485</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.000746418346111897</v>
+        <v>-0.00446122289397388</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.0011689106411044</v>
+        <v>-0.0181230053340054</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.00196319216389814</v>
+        <v>-0.132936556880731</v>
       </c>
     </row>
     <row r="133">
@@ -4026,22 +4026,22 @@
         <v>138</v>
       </c>
       <c r="B133" t="n">
-        <v>0.00177700200435468</v>
+        <v>-0.000707331909900875</v>
       </c>
       <c r="C133" t="n">
-        <v>0.00587462668988206</v>
+        <v>-0.0163837456400542</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.00235603399499012</v>
+        <v>0.00140592151005861</v>
       </c>
       <c r="E133" t="n">
-        <v>0.00779366833816614</v>
+        <v>-0.00942976164485681</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.0079291760409716</v>
+        <v>-0.0281597220717033</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.0017248172078208</v>
+        <v>-0.0436677396825602</v>
       </c>
     </row>
     <row r="134">
@@ -4049,22 +4049,22 @@
         <v>139</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.000666290173110687</v>
+        <v>-0.00402022943406505</v>
       </c>
       <c r="C134" t="n">
-        <v>0.00405960339947377</v>
+        <v>-0.0021720604488526</v>
       </c>
       <c r="D134" t="n">
-        <v>0.000119095755193229</v>
+        <v>0.00578485473186406</v>
       </c>
       <c r="E134" t="n">
-        <v>0.00551220375303918</v>
+        <v>-0.0114269888282955</v>
       </c>
       <c r="F134" t="n">
-        <v>0.00097888641213077</v>
+        <v>-0.00507351656361396</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.0101481603013371</v>
+        <v>0.090111504531493</v>
       </c>
     </row>
     <row r="135">
@@ -4072,22 +4072,22 @@
         <v>140</v>
       </c>
       <c r="B135" t="n">
-        <v>0.0172598337747496</v>
+        <v>0.00630567365043033</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0226548593361017</v>
+        <v>-0.0271916287943555</v>
       </c>
       <c r="D135" t="n">
-        <v>0.00214694768652663</v>
+        <v>-0.0114633126796665</v>
       </c>
       <c r="E135" t="n">
-        <v>0.019910093794801</v>
+        <v>-0.0318278728344858</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0745450157215798</v>
+        <v>0.00673209393624788</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.00767996687949579</v>
+        <v>0.0478680868965315</v>
       </c>
     </row>
     <row r="136">
@@ -4095,22 +4095,22 @@
         <v>141</v>
       </c>
       <c r="B136" t="n">
-        <v>0.0118159934623187</v>
+        <v>0.0091515233444982</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0230267966707044</v>
+        <v>-0.0346822009174581</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0163781884594015</v>
+        <v>0.0102159231494646</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0233564177110948</v>
+        <v>-0.0208081615583702</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.00480224543912165</v>
+        <v>-0.0171267454475928</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.00370004953660194</v>
+        <v>0.0917417876768983</v>
       </c>
     </row>
     <row r="137">
@@ -4118,22 +4118,22 @@
         <v>142</v>
       </c>
       <c r="B137" t="n">
-        <v>0.00340466677479596</v>
+        <v>0.0112538267646298</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0110264117343106</v>
+        <v>-0.0235772301910244</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0237172757450305</v>
+        <v>0.0225251032948556</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.00359225699918925</v>
+        <v>-0.0172242632876573</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0183302541250474</v>
+        <v>0.0356519947646334</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.009701871030035</v>
+        <v>-0.134734287456648</v>
       </c>
     </row>
     <row r="138">
@@ -4141,22 +4141,22 @@
         <v>143</v>
       </c>
       <c r="B138" t="n">
-        <v>0.0670460608935422</v>
+        <v>0.00539392881840961</v>
       </c>
       <c r="C138" t="n">
-        <v>0.135144699752478</v>
+        <v>-0.0290105251357674</v>
       </c>
       <c r="D138" t="n">
-        <v>0.0368422346939207</v>
+        <v>0.0100501667305141</v>
       </c>
       <c r="E138" t="n">
-        <v>0.010619742202414</v>
+        <v>0.0126072903997971</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.306493200126455</v>
+        <v>-0.0267247106427512</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.00384634909216469</v>
+        <v>0.0908153969432733</v>
       </c>
     </row>
     <row r="139">
@@ -4164,22 +4164,22 @@
         <v>144</v>
       </c>
       <c r="B139" t="n">
-        <v>0.0298638579703359</v>
+        <v>0.00117193934077849</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0524672410403092</v>
+        <v>-0.034119468087123</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.0398290642225056</v>
+        <v>-0.0126648634652915</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0132185055450613</v>
+        <v>-0.00590892721676485</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.0177489200202719</v>
+        <v>-0.0250800063105067</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.0887265116038656</v>
+        <v>-0.0880124922395717</v>
       </c>
     </row>
     <row r="140">
@@ -4187,22 +4187,22 @@
         <v>145</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.000626288444506857</v>
+        <v>-0.0768668572464956</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0056771737628093</v>
+        <v>-0.0801353303277584</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.00710887980338</v>
+        <v>-0.0241616688201888</v>
       </c>
       <c r="E140" t="n">
-        <v>0.00707983926196736</v>
+        <v>-0.176583962180606</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.00466876615842079</v>
+        <v>-0.118437358294827</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.00115637852974557</v>
+        <v>-0.00668287888591436</v>
       </c>
     </row>
     <row r="141">
@@ -4210,22 +4210,22 @@
         <v>146</v>
       </c>
       <c r="B141" t="n">
-        <v>0.00681665809234117</v>
+        <v>0.313856763331517</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.0133114814410622</v>
+        <v>0.0288033064478646</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0048793794869198</v>
+        <v>-0.151019241840547</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.0120696648261308</v>
+        <v>0.00697757587062522</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.0216068782242133</v>
+        <v>-0.166352097971467</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0022406393624137</v>
+        <v>0.039233682223544</v>
       </c>
     </row>
     <row r="142">
@@ -4233,22 +4233,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="n">
-        <v>0.181035958695915</v>
+        <v>0.0123286847584207</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0483266548060133</v>
+        <v>-0.0349276982796806</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.141768934629497</v>
+        <v>-0.0247938095553362</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.354712757893976</v>
+        <v>0.0364733716579921</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.17031314265697</v>
+        <v>-0.00689905669570953</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0670365459602304</v>
+        <v>0.00152442136626006</v>
       </c>
     </row>
     <row r="143">
@@ -4256,22 +4256,22 @@
         <v>148</v>
       </c>
       <c r="B143" t="n">
-        <v>0.00963964720514851</v>
+        <v>0.04095289526286</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.0112105791235465</v>
+        <v>-0.0145368468356082</v>
       </c>
       <c r="D143" t="n">
-        <v>0.0193509583239014</v>
+        <v>-0.00988947313524216</v>
       </c>
       <c r="E143" t="n">
-        <v>0.00563594837030048</v>
+        <v>-0.0361506491302771</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0340804708098794</v>
+        <v>0.0446283954238428</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.00298828392003511</v>
+        <v>0.110506827519375</v>
       </c>
     </row>
     <row r="144">
@@ -4279,22 +4279,22 @@
         <v>149</v>
       </c>
       <c r="B144" t="n">
-        <v>0.00260584839374549</v>
+        <v>0.239843595158932</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.00622120191857777</v>
+        <v>0.0230257412724803</v>
       </c>
       <c r="D144" t="n">
-        <v>0.00628793522447276</v>
+        <v>-0.0213481112316045</v>
       </c>
       <c r="E144" t="n">
-        <v>0.00551166690087429</v>
+        <v>-0.152980167029774</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.00600651131802778</v>
+        <v>0.0900904769824454</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.000140728566538859</v>
+        <v>-0.017715265611388</v>
       </c>
     </row>
     <row r="145">
@@ -4302,22 +4302,22 @@
         <v>150</v>
       </c>
       <c r="B145" t="n">
-        <v>0.0272227615940719</v>
+        <v>0.00769012493213039</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0286987660798666</v>
+        <v>-0.0256962683773861</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.00348453688466928</v>
+        <v>-0.00660448741682842</v>
       </c>
       <c r="E145" t="n">
-        <v>0.0278637350473381</v>
+        <v>-0.00974522854986658</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.00695326412232936</v>
+        <v>-0.0184029807305374</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.00386772730870533</v>
+        <v>-0.0896878599438543</v>
       </c>
     </row>
     <row r="146">
@@ -4325,22 +4325,22 @@
         <v>151</v>
       </c>
       <c r="B146" t="n">
-        <v>0.0991941636850992</v>
+        <v>0.0113824040029047</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0918450633913323</v>
+        <v>-0.039748293937046</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.0177180953046246</v>
+        <v>-0.0139742254474733</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.00506344465012922</v>
+        <v>-0.00889057423421992</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0663877875013112</v>
+        <v>-0.00945366289324713</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.127888755771777</v>
+        <v>0.00375028430585353</v>
       </c>
     </row>
     <row r="147">
@@ -4394,22 +4394,22 @@
         <v>154</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0112482495306065</v>
+        <v>0.0716727641892187</v>
       </c>
       <c r="C149" t="n">
-        <v>0.000338853443320918</v>
+        <v>-0.063301906073406</v>
       </c>
       <c r="D149" t="n">
-        <v>0.010127249309704</v>
+        <v>-0.0065978169011253</v>
       </c>
       <c r="E149" t="n">
-        <v>0.00293708960354286</v>
+        <v>-0.0433476019505738</v>
       </c>
       <c r="F149" t="n">
-        <v>0.00846541878849158</v>
+        <v>0.0349096270301796</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.00791303884775178</v>
+        <v>0.0231163887022238</v>
       </c>
     </row>
     <row r="150">
@@ -4417,22 +4417,22 @@
         <v>155</v>
       </c>
       <c r="B150" t="n">
-        <v>0.0105311573127771</v>
+        <v>0.0323462625721955</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.00812463134906654</v>
+        <v>-0.0223677646956597</v>
       </c>
       <c r="D150" t="n">
-        <v>0.00364851880686679</v>
+        <v>-0.0237926721639066</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.00259858310675017</v>
+        <v>0.00360138306846486</v>
       </c>
       <c r="F150" t="n">
-        <v>0.000700420754353983</v>
+        <v>-0.00742150933800261</v>
       </c>
       <c r="G150" t="n">
-        <v>0.00351959092305932</v>
+        <v>-0.130769486204934</v>
       </c>
     </row>
     <row r="151">
@@ -4440,22 +4440,22 @@
         <v>156</v>
       </c>
       <c r="B151" t="n">
-        <v>0.00618797979361469</v>
+        <v>0.010569973277645</v>
       </c>
       <c r="C151" t="n">
-        <v>0.00325874650453611</v>
+        <v>-0.0251548764698937</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.00126350883983666</v>
+        <v>-0.0127116663882189</v>
       </c>
       <c r="E151" t="n">
-        <v>0.00165979077801771</v>
+        <v>-0.00602850375012164</v>
       </c>
       <c r="F151" t="n">
-        <v>0.00258049004706912</v>
+        <v>-0.0112833328019576</v>
       </c>
       <c r="G151" t="n">
-        <v>0.00728044248617153</v>
+        <v>0.000586649691871163</v>
       </c>
     </row>
     <row r="152">
@@ -4463,22 +4463,22 @@
         <v>157</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0120014257226593</v>
+        <v>0.275730656573302</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.0137632515034755</v>
+        <v>-0.0258152712970385</v>
       </c>
       <c r="D152" t="n">
-        <v>0.0160799845116612</v>
+        <v>0.0118119446927091</v>
       </c>
       <c r="E152" t="n">
-        <v>0.00863656433958758</v>
+        <v>-0.178246442077461</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.0112407320631474</v>
+        <v>0.284963744790194</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.00358059042301921</v>
+        <v>-0.038010481133059</v>
       </c>
     </row>
     <row r="153">
@@ -4486,22 +4486,22 @@
         <v>158</v>
       </c>
       <c r="B153" t="n">
-        <v>0.00877773651707827</v>
+        <v>0.03630314984074</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.00344182837054835</v>
+        <v>-0.0285378657044345</v>
       </c>
       <c r="D153" t="n">
-        <v>0.00566942276928862</v>
+        <v>-0.0147695612479632</v>
       </c>
       <c r="E153" t="n">
-        <v>0.00927482616313892</v>
+        <v>-0.0144150257050714</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.00452301177334719</v>
+        <v>-0.0334105842595635</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.00993473693356438</v>
+        <v>-0.0181160016597424</v>
       </c>
     </row>
     <row r="154">
@@ -4509,22 +4509,22 @@
         <v>159</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0187292411073116</v>
+        <v>0.0252057332452632</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.00974047512494816</v>
+        <v>-0.0219190550367118</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.00449715249458009</v>
+        <v>-0.0325599497885203</v>
       </c>
       <c r="E154" t="n">
-        <v>0.0195073234017533</v>
+        <v>-0.0265162941470842</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0307056080978394</v>
+        <v>-0.0178362898394223</v>
       </c>
       <c r="G154" t="n">
-        <v>0.00507013863354286</v>
+        <v>-0.0401979143482668</v>
       </c>
     </row>
     <row r="155">
@@ -4532,22 +4532,22 @@
         <v>160</v>
       </c>
       <c r="B155" t="n">
-        <v>0.0117231683011696</v>
+        <v>0.00131445719758808</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0258700368499595</v>
+        <v>-0.024854222947092</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.0114354147959633</v>
+        <v>-0.0034284326475756</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0340345186454421</v>
+        <v>-0.0158177176411496</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.0199192459420113</v>
+        <v>-0.0325270698855993</v>
       </c>
       <c r="G155" t="n">
-        <v>0.016212974373214</v>
+        <v>0.047031508146476</v>
       </c>
     </row>
     <row r="156">
@@ -4555,22 +4555,22 @@
         <v>161</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.0000670098475911104</v>
+        <v>0.134289331038609</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.00176223236827852</v>
+        <v>0.141126104150319</v>
       </c>
       <c r="D156" t="n">
-        <v>0.00220056497733823</v>
+        <v>0.228191303736618</v>
       </c>
       <c r="E156" t="n">
-        <v>0.000690889897220588</v>
+        <v>0.0601418932465719</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.00454014882816902</v>
+        <v>-0.207801658878756</v>
       </c>
       <c r="G156" t="n">
-        <v>0.000173506474094272</v>
+        <v>0.0102436628066197</v>
       </c>
     </row>
     <row r="157">
@@ -4578,22 +4578,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="n">
-        <v>0.0000568818437036788</v>
+        <v>-0.0140076311595171</v>
       </c>
       <c r="C157" t="n">
-        <v>0.00105189150028275</v>
+        <v>-0.0185973187773954</v>
       </c>
       <c r="D157" t="n">
-        <v>0.00246269507504479</v>
+        <v>0.207227079200689</v>
       </c>
       <c r="E157" t="n">
-        <v>0.00661435763522369</v>
+        <v>-0.272568120973264</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.00262845887034633</v>
+        <v>-0.450438765905678</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.00155441579480694</v>
+        <v>0.00069804515976577</v>
       </c>
     </row>
     <row r="158">
@@ -4601,22 +4601,22 @@
         <v>163</v>
       </c>
       <c r="B158" t="n">
-        <v>0.00634406175542747</v>
+        <v>0.0135455556933377</v>
       </c>
       <c r="C158" t="n">
-        <v>0.00275648842205387</v>
+        <v>-0.0242448586669253</v>
       </c>
       <c r="D158" t="n">
-        <v>0.00338360383334484</v>
+        <v>-0.0000511175888186211</v>
       </c>
       <c r="E158" t="n">
-        <v>0.00174781817876637</v>
+        <v>0.00903254121541002</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.0161921314763572</v>
+        <v>-0.0242711726894863</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.000306183257210794</v>
+        <v>0.000487539656902435</v>
       </c>
     </row>
     <row r="159">
@@ -4624,22 +4624,22 @@
         <v>164</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0118350445821381</v>
+        <v>0.0756023172089219</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.00938127788226899</v>
+        <v>-0.0279033355593058</v>
       </c>
       <c r="D159" t="n">
-        <v>0.0239516768425645</v>
+        <v>0.00324609401393094</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0145674139406326</v>
+        <v>-0.0514019953908408</v>
       </c>
       <c r="F159" t="n">
-        <v>0.00759329079421831</v>
+        <v>0.0394286576591415</v>
       </c>
       <c r="G159" t="n">
-        <v>0.00485389242197789</v>
+        <v>0.109468647067364</v>
       </c>
     </row>
     <row r="160">
@@ -4647,22 +4647,22 @@
         <v>165</v>
       </c>
       <c r="B160" t="n">
-        <v>0.0509481876786755</v>
+        <v>0.00804547293343398</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0672077562410732</v>
+        <v>-0.0261185571826339</v>
       </c>
       <c r="D160" t="n">
-        <v>0.0289655495232489</v>
+        <v>-0.000860285832822755</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0536897047572403</v>
+        <v>-0.0121553858588616</v>
       </c>
       <c r="F160" t="n">
-        <v>0.00765940736892172</v>
+        <v>-0.0111705848740072</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.02940229914089</v>
+        <v>-0.133584017269234</v>
       </c>
     </row>
     <row r="161">
@@ -4670,22 +4670,22 @@
         <v>166</v>
       </c>
       <c r="B161" t="n">
-        <v>-0.0000330311416544842</v>
+        <v>0.05921219389588</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.000623465961111707</v>
+        <v>0.103678238060376</v>
       </c>
       <c r="D161" t="n">
-        <v>0.0003418580164108</v>
+        <v>0.0388421377737683</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.000502295205747126</v>
+        <v>0.211869256971371</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.00115713680686755</v>
+        <v>-0.00126100488657701</v>
       </c>
       <c r="G161" t="n">
-        <v>0.000127198903876903</v>
+        <v>-0.00938885395942997</v>
       </c>
     </row>
     <row r="162">
@@ -4693,22 +4693,22 @@
         <v>167</v>
       </c>
       <c r="B162" t="n">
-        <v>0.00051130724266848</v>
+        <v>0.0119802055364456</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0080085620064794</v>
+        <v>-0.00719967758988814</v>
       </c>
       <c r="D162" t="n">
-        <v>0.0269112983854185</v>
+        <v>0.0617692393189657</v>
       </c>
       <c r="E162" t="n">
-        <v>0.0406391770212826</v>
+        <v>-0.0352848548327605</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.0306081209782896</v>
+        <v>-0.0524072667938247</v>
       </c>
       <c r="G162" t="n">
-        <v>-0.0164151094731614</v>
+        <v>0.045087396443126</v>
       </c>
     </row>
     <row r="163">
@@ -4716,22 +4716,22 @@
         <v>168</v>
       </c>
       <c r="B163" t="n">
-        <v>0.00857627548396615</v>
+        <v>0.0228971976097806</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0164179634932111</v>
+        <v>-0.0759280161201655</v>
       </c>
       <c r="D163" t="n">
-        <v>0.017193065567938</v>
+        <v>0.0359089161231808</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.000984271920343123</v>
+        <v>-0.00909077141617366</v>
       </c>
       <c r="F163" t="n">
-        <v>0.000934811895458644</v>
+        <v>0.00818659323652816</v>
       </c>
       <c r="G163" t="n">
-        <v>-0.00684725695178056</v>
+        <v>0.0201157436286898</v>
       </c>
     </row>
     <row r="164">
@@ -4739,22 +4739,22 @@
         <v>169</v>
       </c>
       <c r="B164" t="n">
-        <v>0.0000997717705764352</v>
+        <v>0.194572083055346</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.00600261597595195</v>
+        <v>0.127486529625524</v>
       </c>
       <c r="D164" t="n">
-        <v>0.000444665259143548</v>
+        <v>-0.12008712775504</v>
       </c>
       <c r="E164" t="n">
-        <v>0.00247181327544244</v>
+        <v>-0.180890457054034</v>
       </c>
       <c r="F164" t="n">
-        <v>0.00647897850889503</v>
+        <v>0.0557591658429752</v>
       </c>
       <c r="G164" t="n">
-        <v>0.00185417155100606</v>
+        <v>0.0496565070502339</v>
       </c>
     </row>
     <row r="165">
@@ -4762,22 +4762,22 @@
         <v>170</v>
       </c>
       <c r="B165" t="n">
-        <v>0.0166161647929199</v>
+        <v>-0.00318934750908519</v>
       </c>
       <c r="C165" t="n">
-        <v>0.050131286082626</v>
+        <v>-0.0143178273458585</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.0574034303966701</v>
+        <v>-0.00838839475980648</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.0542758496258108</v>
+        <v>0.00883409368038521</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.0166317062966037</v>
+        <v>-0.00303871323102027</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.010321314937343</v>
+        <v>0.134966746486175</v>
       </c>
     </row>
     <row r="166">
@@ -4785,22 +4785,22 @@
         <v>171</v>
       </c>
       <c r="B166" t="n">
-        <v>0.00419935515416394</v>
+        <v>0.00535810106262242</v>
       </c>
       <c r="C166" t="n">
-        <v>0.00966620185198714</v>
+        <v>-0.0206305835598782</v>
       </c>
       <c r="D166" t="n">
-        <v>0.0081347374264751</v>
+        <v>0.00606923941626352</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0109910303668937</v>
+        <v>-0.0220376154566832</v>
       </c>
       <c r="F166" t="n">
-        <v>0.00821711214278575</v>
+        <v>-0.00289270388505604</v>
       </c>
       <c r="G166" t="n">
-        <v>-0.00207477138839697</v>
+        <v>0.0884932236683335</v>
       </c>
     </row>
     <row r="167">
@@ -4808,22 +4808,22 @@
         <v>172</v>
       </c>
       <c r="B167" t="n">
-        <v>-0.000466886913684044</v>
+        <v>-0.0204461246144318</v>
       </c>
       <c r="C167" t="n">
-        <v>0.00648972255164365</v>
+        <v>-0.0265654865241478</v>
       </c>
       <c r="D167" t="n">
-        <v>0.000412105681493875</v>
+        <v>0.0246342797510027</v>
       </c>
       <c r="E167" t="n">
-        <v>0.00528916535455457</v>
+        <v>-0.0514343796538591</v>
       </c>
       <c r="F167" t="n">
-        <v>0.00110837260879964</v>
+        <v>-0.0162842389271702</v>
       </c>
       <c r="G167" t="n">
-        <v>-0.00331823116585834</v>
+        <v>-0.0678586414003098</v>
       </c>
     </row>
     <row r="168">
@@ -4831,22 +4831,22 @@
         <v>173</v>
       </c>
       <c r="B168" t="n">
-        <v>0.00964935773906423</v>
+        <v>0.108094922544286</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.00784618238793292</v>
+        <v>-0.0339966605457714</v>
       </c>
       <c r="D168" t="n">
-        <v>0.0179158484666209</v>
+        <v>0.00914318971006151</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0138905800072683</v>
+        <v>-0.05165760557987</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.00902722667279134</v>
+        <v>0.0123566251507213</v>
       </c>
       <c r="G168" t="n">
-        <v>0.00285891587769207</v>
+        <v>0.0500412371366979</v>
       </c>
     </row>
     <row r="169">
@@ -4854,22 +4854,22 @@
         <v>174</v>
       </c>
       <c r="B169" t="n">
-        <v>0.177485489539727</v>
+        <v>0.00270270443583085</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0697799160538293</v>
+        <v>-0.0154034305309216</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.502246529023631</v>
+        <v>-0.0248867632936474</v>
       </c>
       <c r="E169" t="n">
-        <v>0.322991095745145</v>
+        <v>-0.011239409351952</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0537434500084416</v>
+        <v>-0.0305063270807039</v>
       </c>
       <c r="G169" t="n">
-        <v>-0.14200185043886</v>
+        <v>0.0469565904123897</v>
       </c>
     </row>
     <row r="170">
@@ -4877,22 +4877,22 @@
         <v>175</v>
       </c>
       <c r="B170" t="n">
-        <v>0.000416128304571162</v>
+        <v>-0.0120893882551543</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0105814195921214</v>
+        <v>-0.0274594215641991</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.00506839294903951</v>
+        <v>0.0224354703790115</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0247956111618424</v>
+        <v>-0.038064376653763</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.0269602204540406</v>
+        <v>-0.123458533861636</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.00654712161761308</v>
+        <v>-0.0128942362094502</v>
       </c>
     </row>
     <row r="171">
@@ -4900,22 +4900,22 @@
         <v>176</v>
       </c>
       <c r="B171" t="n">
-        <v>0.00659149019464204</v>
+        <v>0.0101674981543915</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.00104918237247784</v>
+        <v>-0.0165023705725229</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.00786350147587172</v>
+        <v>-0.0212626244363961</v>
       </c>
       <c r="E171" t="n">
-        <v>0.00545375458729934</v>
+        <v>-0.00214803253489618</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.00427907720113718</v>
+        <v>-0.0282672412381016</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.00179212303538175</v>
+        <v>-0.0395642038249428</v>
       </c>
     </row>
     <row r="172">
@@ -4923,22 +4923,22 @@
         <v>177</v>
       </c>
       <c r="B172" t="n">
-        <v>0.00913540885943141</v>
+        <v>0.0132434389748127</v>
       </c>
       <c r="C172" t="n">
-        <v>0.00522384155686834</v>
+        <v>-0.0255879456924688</v>
       </c>
       <c r="D172" t="n">
-        <v>0.00487535882121258</v>
+        <v>-0.00486212513919511</v>
       </c>
       <c r="E172" t="n">
-        <v>0.00616844789321482</v>
+        <v>-0.00831799814247122</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.000258167255563338</v>
+        <v>-0.0118745097488933</v>
       </c>
       <c r="G172" t="n">
-        <v>0.00766506736233169</v>
+        <v>-0.0866382461306559</v>
       </c>
     </row>
     <row r="173">
@@ -4946,22 +4946,22 @@
         <v>178</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0461828882334556</v>
+        <v>0.00047612890357712</v>
       </c>
       <c r="C173" t="n">
-        <v>0.171008203189299</v>
+        <v>-0.0662851729592737</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0751482834123189</v>
+        <v>0.0251550271692152</v>
       </c>
       <c r="E173" t="n">
-        <v>0.153929850997129</v>
+        <v>-0.0532095769294253</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.00594286051613456</v>
+        <v>-0.0309362742573712</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.0563766001776604</v>
+        <v>0.00281209161834143</v>
       </c>
     </row>
     <row r="174">
@@ -4969,22 +4969,22 @@
         <v>179</v>
       </c>
       <c r="B174" t="n">
-        <v>0.00578391328584609</v>
+        <v>-0.00138845445336114</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0210105218551326</v>
+        <v>-0.0257203388089959</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.00504711301969409</v>
+        <v>0.00539311586116518</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0180880038849418</v>
+        <v>-0.00722531991160824</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.0280321843870815</v>
+        <v>-0.0348312614104276</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.00159553344648931</v>
+        <v>0.0911850693108336</v>
       </c>
     </row>
     <row r="175">
@@ -4992,22 +4992,22 @@
         <v>180</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0089100326063758</v>
+        <v>0.00724228565063526</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0319570138217266</v>
+        <v>-0.0506810917010356</v>
       </c>
       <c r="D175" t="n">
-        <v>0.027907255554831</v>
+        <v>0.0301868055361633</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0316767552205459</v>
+        <v>-0.045493109980518</v>
       </c>
       <c r="F175" t="n">
-        <v>0.00444437736644661</v>
+        <v>-0.0120271506266185</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.00798127143198649</v>
+        <v>0.0497284598303042</v>
       </c>
     </row>
     <row r="176">
@@ -5015,22 +5015,22 @@
         <v>181</v>
       </c>
       <c r="B176" t="n">
-        <v>0.432001100785313</v>
+        <v>0.0334465438449992</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0527496490273628</v>
+        <v>-0.0505794164392866</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.0365040806971336</v>
+        <v>-0.0301924200972623</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0103497596387269</v>
+        <v>-0.0102033933027758</v>
       </c>
       <c r="F176" t="n">
-        <v>0.149527982260969</v>
+        <v>-0.0229377456615612</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.123034410723278</v>
+        <v>0.00390723096747295</v>
       </c>
     </row>
     <row r="177">
@@ -5038,22 +5038,22 @@
         <v>182</v>
       </c>
       <c r="B177" t="n">
-        <v>0.151558063882118</v>
+        <v>0.0109826905254251</v>
       </c>
       <c r="C177" t="n">
-        <v>0.191828691873905</v>
+        <v>-0.0485714521013111</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.0155310170860749</v>
+        <v>-0.0053684856578767</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0714371895147281</v>
+        <v>-0.00692304912568427</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.109500657581288</v>
+        <v>-0.030719149555556</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0208555080337293</v>
+        <v>-0.0875292326936379</v>
       </c>
     </row>
     <row r="178">
@@ -5153,22 +5153,22 @@
         <v>187</v>
       </c>
       <c r="B182" t="n">
-        <v>0.23546293139579</v>
+        <v>0.0331684492498082</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.148297653708274</v>
+        <v>-0.0275495664939364</v>
       </c>
       <c r="D182" t="n">
-        <v>0.0649481900099084</v>
+        <v>-0.025040733605349</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.19121062873184</v>
+        <v>0.0145058676571732</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.00959689275323941</v>
+        <v>-0.000365938723268601</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.0432602530277824</v>
+        <v>0.136110681511947</v>
       </c>
     </row>
     <row r="183">
@@ -5199,22 +5199,22 @@
         <v>189</v>
       </c>
       <c r="B184" t="n">
-        <v>0.00102485096208216</v>
+        <v>0.181926261039064</v>
       </c>
       <c r="C184" t="n">
-        <v>0.00425295161183142</v>
+        <v>-0.197565826621037</v>
       </c>
       <c r="D184" t="n">
-        <v>0.0127747428762718</v>
+        <v>0.351430454773742</v>
       </c>
       <c r="E184" t="n">
-        <v>0.00511743189613419</v>
+        <v>0.061008650316839</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.00297262028526757</v>
+        <v>0.165207852638457</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.00298180912977799</v>
+        <v>-0.00147991661918554</v>
       </c>
     </row>
     <row r="185">
@@ -5222,22 +5222,22 @@
         <v>190</v>
       </c>
       <c r="B185" t="n">
-        <v>0.00636689459335823</v>
+        <v>0.0602003340719986</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.00978011724450418</v>
+        <v>-0.00333963573339389</v>
       </c>
       <c r="D185" t="n">
-        <v>0.00248768987845194</v>
+        <v>-0.0519661749653653</v>
       </c>
       <c r="E185" t="n">
-        <v>0.015656550046684</v>
+        <v>-0.0638021723951743</v>
       </c>
       <c r="F185" t="n">
-        <v>0.00992017545089888</v>
+        <v>-0.0532852784078828</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.000238573094607598</v>
+        <v>-0.0217704371466962</v>
       </c>
     </row>
     <row r="186">
@@ -5291,22 +5291,22 @@
         <v>193</v>
       </c>
       <c r="B188" t="n">
-        <v>0.00910645955343</v>
+        <v>-0.00203514569817034</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0236140415259067</v>
+        <v>-0.00615492910645531</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.0691616036676597</v>
+        <v>-0.00452373359101052</v>
       </c>
       <c r="E188" t="n">
-        <v>0.0518906842302322</v>
+        <v>0.00504771330302489</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.155522451969114</v>
+        <v>-0.0342979613175415</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.00955962850109909</v>
+        <v>0.0450165425486919</v>
       </c>
     </row>
     <row r="189">
@@ -5314,22 +5314,22 @@
         <v>194</v>
       </c>
       <c r="B189" t="n">
-        <v>0.000383805272045213</v>
+        <v>-0.00485838695151525</v>
       </c>
       <c r="C189" t="n">
-        <v>0.00368645996195358</v>
+        <v>-0.0176177866150858</v>
       </c>
       <c r="D189" t="n">
-        <v>0.00047328696238881</v>
+        <v>-0.00171497434194402</v>
       </c>
       <c r="E189" t="n">
-        <v>0.00511041680726011</v>
+        <v>-0.0521907585493003</v>
       </c>
       <c r="F189" t="n">
-        <v>0.011582060836847</v>
+        <v>0.0109606908309654</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.00229848673499673</v>
+        <v>-0.0213804289522527</v>
       </c>
     </row>
     <row r="190">
@@ -5337,22 +5337,22 @@
         <v>195</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.00261552298252081</v>
+        <v>-0.0376203582811347</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0116993335221005</v>
+        <v>-0.0177241351364623</v>
       </c>
       <c r="D190" t="n">
-        <v>0.0051783172166322</v>
+        <v>0.0491925916066678</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.00801434803481489</v>
+        <v>-0.0254284032292113</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0110446589459137</v>
+        <v>0.0662604430547759</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.0061771906329297</v>
+        <v>-0.071382484274527</v>
       </c>
     </row>
     <row r="191">
@@ -5360,22 +5360,22 @@
         <v>196</v>
       </c>
       <c r="B191" t="n">
-        <v>0.0915100712633732</v>
+        <v>0.00333869125641026</v>
       </c>
       <c r="C191" t="n">
-        <v>0.160375535023153</v>
+        <v>-0.0310978952100145</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.0502394437595275</v>
+        <v>-0.00950350401865012</v>
       </c>
       <c r="E191" t="n">
-        <v>0.196664231511087</v>
+        <v>-0.0293537592177329</v>
       </c>
       <c r="F191" t="n">
-        <v>0.125544360714218</v>
+        <v>-0.0201341562441764</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.139165573872339</v>
+        <v>-0.0883553405295857</v>
       </c>
     </row>
     <row r="192">
@@ -5383,22 +5383,22 @@
         <v>197</v>
       </c>
       <c r="B192" t="n">
-        <v>0.00145144923634991</v>
+        <v>0.0861464650590501</v>
       </c>
       <c r="C192" t="n">
-        <v>0.000403545583866841</v>
+        <v>-0.232921827251147</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.00119804730598125</v>
+        <v>-0.205421169785922</v>
       </c>
       <c r="E192" t="n">
-        <v>-0.00162157954746825</v>
+        <v>0.0772427637429022</v>
       </c>
       <c r="F192" t="n">
-        <v>0.000916567976754431</v>
+        <v>-0.0236078456557613</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.000263273795135522</v>
+        <v>0.0104582188567969</v>
       </c>
     </row>
     <row r="193">
@@ -5452,22 +5452,22 @@
         <v>200</v>
       </c>
       <c r="B195" t="n">
-        <v>0.00424755953094805</v>
+        <v>0.00390364114465595</v>
       </c>
       <c r="C195" t="n">
-        <v>0.0123160350118441</v>
+        <v>-0.0319283292473076</v>
       </c>
       <c r="D195" t="n">
-        <v>0.00596246145141118</v>
+        <v>0.00846929714750262</v>
       </c>
       <c r="E195" t="n">
-        <v>0.0206491733967214</v>
+        <v>-0.0441736720971653</v>
       </c>
       <c r="F195" t="n">
-        <v>0.00510934210931358</v>
+        <v>-0.021621880088475</v>
       </c>
       <c r="G195" t="n">
-        <v>-0.0124150674520784</v>
+        <v>0.000763183225105008</v>
       </c>
     </row>
     <row r="196">
@@ -5475,22 +5475,22 @@
         <v>201</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0144933160115944</v>
+        <v>0.0176056889003543</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.00960753808261428</v>
+        <v>-0.0123815949380486</v>
       </c>
       <c r="D196" t="n">
-        <v>0.00961691965449333</v>
+        <v>-0.0107688608537126</v>
       </c>
       <c r="E196" t="n">
-        <v>0.0218876765115389</v>
+        <v>-0.0141929365141025</v>
       </c>
       <c r="F196" t="n">
-        <v>0.00994215052303792</v>
+        <v>-0.011862491784286</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.0197932905403559</v>
+        <v>-0.0873264911460706</v>
       </c>
     </row>
     <row r="197">
@@ -5498,22 +5498,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="n">
-        <v>0.0015506113788342</v>
+        <v>-0.00870073843305969</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0153254771516578</v>
+        <v>-0.0510439015239408</v>
       </c>
       <c r="D197" t="n">
-        <v>0.00664763245711074</v>
+        <v>0.0316629948948649</v>
       </c>
       <c r="E197" t="n">
-        <v>0.00949767227690404</v>
+        <v>-0.0475979359034207</v>
       </c>
       <c r="F197" t="n">
-        <v>0.00171404175778145</v>
+        <v>-0.0132890654163082</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.00508203475049465</v>
+        <v>-0.0701590586818464</v>
       </c>
     </row>
     <row r="198">
@@ -5521,22 +5521,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="n">
-        <v>0.00816882033618729</v>
+        <v>-0.00640303897805457</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0338812870931123</v>
+        <v>-0.0313012640456741</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.0190434211505907</v>
+        <v>-0.00474935060073387</v>
       </c>
       <c r="E198" t="n">
-        <v>0.00470283458959791</v>
+        <v>-0.00719271921703221</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.00934450529943042</v>
+        <v>-0.0195174460380881</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0358961089743341</v>
+        <v>-0.0423377638580738</v>
       </c>
     </row>
     <row r="199">
@@ -5544,22 +5544,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="n">
-        <v>0.0130427277400189</v>
+        <v>-0.00107163900483453</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0311996818406103</v>
+        <v>-0.0217792000279665</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.0189316426385313</v>
+        <v>-0.0109448855072378</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0323263881008208</v>
+        <v>-0.0266356169245854</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0526981274722966</v>
+        <v>-0.00831144604062003</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.0195634440589183</v>
+        <v>0.0498670386775258</v>
       </c>
     </row>
     <row r="200">
@@ -5567,22 +5567,22 @@
         <v>205</v>
       </c>
       <c r="B200" t="n">
-        <v>0.00248737180433396</v>
+        <v>-0.0157465445103613</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0136533473184637</v>
+        <v>-0.0401503251227725</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.0155170524712427</v>
+        <v>-0.0152622515779279</v>
       </c>
       <c r="E200" t="n">
-        <v>0.00116991265301483</v>
+        <v>-0.00106653384693081</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.0114807340918524</v>
+        <v>-0.0420289806758276</v>
       </c>
       <c r="G200" t="n">
-        <v>0.00839558235307069</v>
+        <v>-0.0869047169750142</v>
       </c>
     </row>
     <row r="201">
@@ -5590,22 +5590,22 @@
         <v>206</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.00990601672790143</v>
+        <v>-0.0115599417038178</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.0164634487361578</v>
+        <v>0.0190729901965494</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.0695275909956026</v>
+        <v>-0.0210964703345467</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0121866996788824</v>
+        <v>0.0109209268489965</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.0422317469355837</v>
+        <v>-0.0317507954808862</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.0110856777586373</v>
+        <v>0.000391379757051251</v>
       </c>
     </row>
     <row r="202">
@@ -5613,22 +5613,22 @@
         <v>207</v>
       </c>
       <c r="B202" t="n">
-        <v>0.0327886208983892</v>
+        <v>0.0222169794718591</v>
       </c>
       <c r="C202" t="n">
-        <v>0.0142344558325063</v>
+        <v>-0.046865541845208</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.00617108055782512</v>
+        <v>-0.0206795327343297</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0114693562200403</v>
+        <v>-0.00859891260017697</v>
       </c>
       <c r="F202" t="n">
-        <v>-0.00578764964488879</v>
+        <v>-0.0337758262152668</v>
       </c>
       <c r="G202" t="n">
-        <v>0.00871077722341617</v>
+        <v>0.00481038816814823</v>
       </c>
     </row>
     <row r="203">
@@ -5636,22 +5636,22 @@
         <v>208</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0201618828326375</v>
+        <v>0.0195815087423474</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.0128767833919875</v>
+        <v>-0.0129874861144194</v>
       </c>
       <c r="D203" t="n">
-        <v>0.0114349393804533</v>
+        <v>-0.0106638825123517</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0429274998287957</v>
+        <v>-0.0156341486874851</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.00864673321768085</v>
+        <v>-0.0266692726048657</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.0238992744997627</v>
+        <v>0.00116854720069754</v>
       </c>
     </row>
     <row r="204">
@@ -5659,22 +5659,22 @@
         <v>209</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.0123939375096805</v>
+        <v>-0.0133509041912366</v>
       </c>
       <c r="C204" t="n">
-        <v>0.0471005748483835</v>
+        <v>-0.000312377866283413</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.0803511360767711</v>
+        <v>-0.000113855478896636</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0915695997158004</v>
+        <v>-0.0149014421800251</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.0787789813346183</v>
+        <v>-0.037219716984718</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.0254066714123147</v>
+        <v>-0.0442897273503462</v>
       </c>
     </row>
     <row r="205">
@@ -5682,22 +5682,22 @@
         <v>210</v>
       </c>
       <c r="B205" t="n">
-        <v>0.0113875189609161</v>
+        <v>-0.0169323211322007</v>
       </c>
       <c r="C205" t="n">
-        <v>0.0819856071281044</v>
+        <v>-0.0332534750486684</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.10293525624401</v>
+        <v>-0.0181484061334641</v>
       </c>
       <c r="E205" t="n">
-        <v>0.00533488706205694</v>
+        <v>-0.00612161707280465</v>
       </c>
       <c r="F205" t="n">
-        <v>-0.0349892344694963</v>
+        <v>-0.0306094349475299</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.0442347268186635</v>
+        <v>-0.0414312663064985</v>
       </c>
     </row>
     <row r="206">
@@ -5705,22 +5705,22 @@
         <v>211</v>
       </c>
       <c r="B206" t="n">
-        <v>0.0238615911638873</v>
+        <v>0.025883678675822</v>
       </c>
       <c r="C206" t="n">
-        <v>0.0139821038593382</v>
+        <v>-0.0669833615570625</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.00148893884296321</v>
+        <v>-0.0344711444490173</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.0271296821922656</v>
+        <v>-0.0154997690162444</v>
       </c>
       <c r="F206" t="n">
-        <v>0.052182696274707</v>
+        <v>0.044333352170312</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.00996021914361922</v>
+        <v>0.00187186046841901</v>
       </c>
     </row>
     <row r="207">
@@ -5728,22 +5728,22 @@
         <v>212</v>
       </c>
       <c r="B207" t="n">
-        <v>0.0073869231260798</v>
+        <v>0.00444773335667908</v>
       </c>
       <c r="C207" t="n">
-        <v>0.00753580793973576</v>
+        <v>-0.0430650023446195</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.0104177111666386</v>
+        <v>-0.0258620384500507</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.00973219502697356</v>
+        <v>0.0216295407010995</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.00531304354811059</v>
+        <v>-0.0191288440718004</v>
       </c>
       <c r="G207" t="n">
-        <v>-0.00832686080019926</v>
+        <v>-0.0432318465716932</v>
       </c>
     </row>
     <row r="208">
@@ -5751,22 +5751,22 @@
         <v>213</v>
       </c>
       <c r="B208" t="n">
-        <v>0.000291514121014574</v>
+        <v>0.00131701408300262</v>
       </c>
       <c r="C208" t="n">
-        <v>0.000181421952304884</v>
+        <v>-0.145294440180627</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.000511785588975266</v>
+        <v>-0.143429520159449</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.000336900833122235</v>
+        <v>0.100163813175065</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.00014914598041741</v>
+        <v>-0.136655064922698</v>
       </c>
       <c r="G208" t="n">
-        <v>0.0000157773801710185</v>
+        <v>0.00612050472243574</v>
       </c>
     </row>
     <row r="209">
@@ -5774,22 +5774,22 @@
         <v>214</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.00650092767063264</v>
+        <v>-0.034761092949346</v>
       </c>
       <c r="C209" t="n">
-        <v>0.0125886763423254</v>
+        <v>0.00751495229779699</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.0220588408359583</v>
+        <v>-0.00655592837665806</v>
       </c>
       <c r="E209" t="n">
-        <v>0.00477513465228838</v>
+        <v>-0.0282906367159568</v>
       </c>
       <c r="F209" t="n">
-        <v>0.0165894314642749</v>
+        <v>0.00187521159657097</v>
       </c>
       <c r="G209" t="n">
-        <v>-0.00474660432906356</v>
+        <v>-0.0901508753566557</v>
       </c>
     </row>
   </sheetData>
